--- a/output/version3/test/15-10/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="C2" t="n">
-        <v>731</v>
+        <v>686</v>
       </c>
       <c r="D2" t="n">
-        <v>784</v>
+        <v>699</v>
       </c>
       <c r="E2" t="n">
+        <v>596</v>
+      </c>
+      <c r="F2" t="n">
+        <v>730</v>
+      </c>
+      <c r="G2" t="n">
+        <v>608</v>
+      </c>
+      <c r="H2" t="n">
+        <v>702</v>
+      </c>
+      <c r="I2" t="n">
+        <v>708</v>
+      </c>
+      <c r="J2" t="n">
         <v>676</v>
       </c>
-      <c r="F2" t="n">
-        <v>611</v>
-      </c>
-      <c r="G2" t="n">
-        <v>774</v>
-      </c>
-      <c r="H2" t="n">
-        <v>614</v>
-      </c>
-      <c r="I2" t="n">
-        <v>661</v>
-      </c>
-      <c r="J2" t="n">
-        <v>699</v>
-      </c>
       <c r="K2" t="n">
-        <v>833</v>
+        <v>741</v>
       </c>
       <c r="L2" t="n">
-        <v>700.2</v>
+        <v>677.5</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>704</v>
+        <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>631</v>
+        <v>789</v>
       </c>
       <c r="D3" t="n">
-        <v>744</v>
+        <v>581</v>
       </c>
       <c r="E3" t="n">
-        <v>748</v>
+        <v>780</v>
       </c>
       <c r="F3" t="n">
-        <v>658</v>
+        <v>706</v>
       </c>
       <c r="G3" t="n">
-        <v>639</v>
+        <v>692</v>
       </c>
       <c r="H3" t="n">
-        <v>809</v>
+        <v>752</v>
       </c>
       <c r="I3" t="n">
-        <v>702</v>
+        <v>638</v>
       </c>
       <c r="J3" t="n">
-        <v>928</v>
+        <v>759</v>
       </c>
       <c r="K3" t="n">
-        <v>910</v>
+        <v>701</v>
       </c>
       <c r="L3" t="n">
-        <v>747.3</v>
+        <v>707.2</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="C4" t="n">
-        <v>665</v>
+        <v>698</v>
       </c>
       <c r="D4" t="n">
-        <v>711</v>
+        <v>795</v>
       </c>
       <c r="E4" t="n">
-        <v>646</v>
+        <v>720</v>
       </c>
       <c r="F4" t="n">
-        <v>631</v>
+        <v>691</v>
       </c>
       <c r="G4" t="n">
-        <v>730</v>
+        <v>608</v>
       </c>
       <c r="H4" t="n">
-        <v>869</v>
+        <v>689</v>
       </c>
       <c r="I4" t="n">
-        <v>619</v>
+        <v>686</v>
       </c>
       <c r="J4" t="n">
-        <v>781</v>
+        <v>713</v>
       </c>
       <c r="K4" t="n">
-        <v>683</v>
+        <v>590</v>
       </c>
       <c r="L4" t="n">
-        <v>697.8</v>
+        <v>686.4</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>725</v>
+        <v>694</v>
       </c>
       <c r="C5" t="n">
-        <v>718</v>
+        <v>681</v>
       </c>
       <c r="D5" t="n">
-        <v>773</v>
+        <v>704</v>
       </c>
       <c r="E5" t="n">
-        <v>738</v>
+        <v>642</v>
       </c>
       <c r="F5" t="n">
+        <v>608</v>
+      </c>
+      <c r="G5" t="n">
+        <v>677</v>
+      </c>
+      <c r="H5" t="n">
+        <v>708</v>
+      </c>
+      <c r="I5" t="n">
+        <v>631</v>
+      </c>
+      <c r="J5" t="n">
         <v>729</v>
       </c>
-      <c r="G5" t="n">
-        <v>713</v>
-      </c>
-      <c r="H5" t="n">
-        <v>701</v>
-      </c>
-      <c r="I5" t="n">
-        <v>640</v>
-      </c>
-      <c r="J5" t="n">
-        <v>670</v>
-      </c>
       <c r="K5" t="n">
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="L5" t="n">
-        <v>706.1</v>
+        <v>675.5</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>634</v>
+        <v>769</v>
       </c>
       <c r="C6" t="n">
-        <v>782</v>
+        <v>660</v>
       </c>
       <c r="D6" t="n">
-        <v>721</v>
+        <v>637</v>
       </c>
       <c r="E6" t="n">
-        <v>647</v>
+        <v>619</v>
       </c>
       <c r="F6" t="n">
-        <v>766</v>
+        <v>650</v>
       </c>
       <c r="G6" t="n">
-        <v>705</v>
+        <v>803</v>
       </c>
       <c r="H6" t="n">
-        <v>810</v>
+        <v>644</v>
       </c>
       <c r="I6" t="n">
-        <v>781</v>
+        <v>664</v>
       </c>
       <c r="J6" t="n">
-        <v>816</v>
+        <v>685</v>
       </c>
       <c r="K6" t="n">
-        <v>760</v>
+        <v>630</v>
       </c>
       <c r="L6" t="n">
-        <v>742.2</v>
+        <v>676.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>678</v>
+        <v>564</v>
       </c>
       <c r="C7" t="n">
-        <v>746</v>
+        <v>623</v>
       </c>
       <c r="D7" t="n">
-        <v>737</v>
+        <v>607</v>
       </c>
       <c r="E7" t="n">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="F7" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G7" t="n">
-        <v>649</v>
+        <v>598</v>
       </c>
       <c r="H7" t="n">
-        <v>708</v>
+        <v>604</v>
       </c>
       <c r="I7" t="n">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="J7" t="n">
-        <v>706</v>
+        <v>603</v>
       </c>
       <c r="K7" t="n">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="L7" t="n">
-        <v>693.2</v>
+        <v>632.7</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>785</v>
+        <v>652</v>
       </c>
       <c r="C8" t="n">
-        <v>785</v>
+        <v>621</v>
       </c>
       <c r="D8" t="n">
-        <v>716</v>
+        <v>650</v>
       </c>
       <c r="E8" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="F8" t="n">
-        <v>743</v>
+        <v>660</v>
       </c>
       <c r="G8" t="n">
-        <v>660</v>
+        <v>597</v>
       </c>
       <c r="H8" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I8" t="n">
-        <v>765</v>
+        <v>729</v>
       </c>
       <c r="J8" t="n">
-        <v>783</v>
+        <v>587</v>
       </c>
       <c r="K8" t="n">
-        <v>875</v>
+        <v>667</v>
       </c>
       <c r="L8" t="n">
-        <v>739.2</v>
+        <v>645.1</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="C9" t="n">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D9" t="n">
-        <v>546</v>
+        <v>586</v>
       </c>
       <c r="E9" t="n">
+        <v>673</v>
+      </c>
+      <c r="F9" t="n">
+        <v>675</v>
+      </c>
+      <c r="G9" t="n">
+        <v>653</v>
+      </c>
+      <c r="H9" t="n">
+        <v>662</v>
+      </c>
+      <c r="I9" t="n">
+        <v>610</v>
+      </c>
+      <c r="J9" t="n">
         <v>700</v>
       </c>
-      <c r="F9" t="n">
-        <v>769</v>
-      </c>
-      <c r="G9" t="n">
-        <v>785</v>
-      </c>
-      <c r="H9" t="n">
-        <v>725</v>
-      </c>
-      <c r="I9" t="n">
-        <v>580</v>
-      </c>
-      <c r="J9" t="n">
-        <v>555</v>
-      </c>
       <c r="K9" t="n">
-        <v>729</v>
+        <v>631</v>
       </c>
       <c r="L9" t="n">
-        <v>671.5</v>
+        <v>646.6</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="C10" t="n">
-        <v>822</v>
+        <v>896</v>
       </c>
       <c r="D10" t="n">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="E10" t="n">
-        <v>826</v>
+        <v>863</v>
       </c>
       <c r="F10" t="n">
-        <v>873</v>
+        <v>735</v>
       </c>
       <c r="G10" t="n">
         <v>820</v>
       </c>
       <c r="H10" t="n">
-        <v>964</v>
+        <v>802</v>
       </c>
       <c r="I10" t="n">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="J10" t="n">
-        <v>865</v>
+        <v>735</v>
       </c>
       <c r="K10" t="n">
-        <v>748</v>
+        <v>766</v>
       </c>
       <c r="L10" t="n">
-        <v>838</v>
+        <v>800.7</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="C11" t="n">
-        <v>864</v>
+        <v>662</v>
       </c>
       <c r="D11" t="n">
-        <v>700</v>
+        <v>724</v>
       </c>
       <c r="E11" t="n">
-        <v>822</v>
+        <v>742</v>
       </c>
       <c r="F11" t="n">
-        <v>798</v>
+        <v>749</v>
       </c>
       <c r="G11" t="n">
-        <v>752</v>
+        <v>649</v>
       </c>
       <c r="H11" t="n">
-        <v>713</v>
+        <v>674</v>
       </c>
       <c r="I11" t="n">
-        <v>658</v>
+        <v>785</v>
       </c>
       <c r="J11" t="n">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="K11" t="n">
-        <v>909</v>
+        <v>771</v>
       </c>
       <c r="L11" t="n">
-        <v>761.7</v>
+        <v>713.8</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="C12" t="n">
-        <v>701</v>
+        <v>650</v>
       </c>
       <c r="D12" t="n">
-        <v>671</v>
+        <v>619</v>
       </c>
       <c r="E12" t="n">
-        <v>761</v>
+        <v>636</v>
       </c>
       <c r="F12" t="n">
-        <v>701</v>
+        <v>624</v>
       </c>
       <c r="G12" t="n">
-        <v>758</v>
+        <v>666</v>
       </c>
       <c r="H12" t="n">
-        <v>686</v>
+        <v>757</v>
       </c>
       <c r="I12" t="n">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="J12" t="n">
-        <v>725</v>
+        <v>592</v>
       </c>
       <c r="K12" t="n">
-        <v>620</v>
+        <v>693</v>
       </c>
       <c r="L12" t="n">
-        <v>702</v>
+        <v>665.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="C13" t="n">
-        <v>837</v>
+        <v>730</v>
       </c>
       <c r="D13" t="n">
-        <v>685</v>
+        <v>793</v>
       </c>
       <c r="E13" t="n">
-        <v>852</v>
+        <v>828</v>
       </c>
       <c r="F13" t="n">
-        <v>722</v>
+        <v>993</v>
       </c>
       <c r="G13" t="n">
-        <v>719</v>
+        <v>861</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="I13" t="n">
-        <v>974</v>
+        <v>827</v>
       </c>
       <c r="J13" t="n">
-        <v>864</v>
+        <v>799</v>
       </c>
       <c r="K13" t="n">
-        <v>878</v>
+        <v>768</v>
       </c>
       <c r="L13" t="n">
-        <v>829.4</v>
+        <v>832.5</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="C14" t="n">
-        <v>774</v>
+        <v>633</v>
       </c>
       <c r="D14" t="n">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="E14" t="n">
-        <v>795</v>
+        <v>686</v>
       </c>
       <c r="F14" t="n">
-        <v>739</v>
+        <v>769</v>
       </c>
       <c r="G14" t="n">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="H14" t="n">
-        <v>792</v>
+        <v>701</v>
       </c>
       <c r="I14" t="n">
-        <v>850</v>
+        <v>704</v>
       </c>
       <c r="J14" t="n">
-        <v>785</v>
+        <v>634</v>
       </c>
       <c r="K14" t="n">
-        <v>817</v>
+        <v>690</v>
       </c>
       <c r="L14" t="n">
-        <v>783.3</v>
+        <v>705.1</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>799</v>
+        <v>757</v>
       </c>
       <c r="C15" t="n">
-        <v>720</v>
+        <v>797</v>
       </c>
       <c r="D15" t="n">
-        <v>739</v>
+        <v>805</v>
       </c>
       <c r="E15" t="n">
-        <v>916</v>
+        <v>676</v>
       </c>
       <c r="F15" t="n">
-        <v>691</v>
+        <v>644</v>
       </c>
       <c r="G15" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="H15" t="n">
-        <v>798</v>
+        <v>748</v>
       </c>
       <c r="I15" t="n">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="J15" t="n">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="K15" t="n">
-        <v>751</v>
+        <v>687</v>
       </c>
       <c r="L15" t="n">
-        <v>766.2</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="C16" t="n">
-        <v>751</v>
+        <v>687</v>
       </c>
       <c r="D16" t="n">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="E16" t="n">
-        <v>871</v>
+        <v>667</v>
       </c>
       <c r="F16" t="n">
-        <v>784</v>
+        <v>843</v>
       </c>
       <c r="G16" t="n">
-        <v>808</v>
+        <v>742</v>
       </c>
       <c r="H16" t="n">
-        <v>653</v>
+        <v>737</v>
       </c>
       <c r="I16" t="n">
-        <v>819</v>
+        <v>651</v>
       </c>
       <c r="J16" t="n">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="K16" t="n">
-        <v>688</v>
+        <v>711</v>
       </c>
       <c r="L16" t="n">
-        <v>756</v>
+        <v>723.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>639</v>
+        <v>749</v>
       </c>
       <c r="C17" t="n">
-        <v>623</v>
+        <v>657</v>
       </c>
       <c r="D17" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="E17" t="n">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="F17" t="n">
-        <v>721</v>
+        <v>681</v>
       </c>
       <c r="G17" t="n">
-        <v>868</v>
+        <v>686</v>
       </c>
       <c r="H17" t="n">
-        <v>687</v>
+        <v>628</v>
       </c>
       <c r="I17" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="J17" t="n">
-        <v>721</v>
+        <v>672</v>
       </c>
       <c r="K17" t="n">
-        <v>704</v>
+        <v>655</v>
       </c>
       <c r="L17" t="n">
-        <v>696.7</v>
+        <v>671.8</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>651</v>
+        <v>778</v>
       </c>
       <c r="C18" t="n">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D18" t="n">
-        <v>711</v>
+        <v>621</v>
       </c>
       <c r="E18" t="n">
-        <v>711</v>
+        <v>673</v>
       </c>
       <c r="F18" t="n">
-        <v>754</v>
+        <v>712</v>
       </c>
       <c r="G18" t="n">
-        <v>745</v>
+        <v>794</v>
       </c>
       <c r="H18" t="n">
-        <v>856</v>
+        <v>829</v>
       </c>
       <c r="I18" t="n">
-        <v>880</v>
+        <v>698</v>
       </c>
       <c r="J18" t="n">
-        <v>987</v>
+        <v>627</v>
       </c>
       <c r="K18" t="n">
-        <v>691</v>
+        <v>655</v>
       </c>
       <c r="L18" t="n">
-        <v>767.9</v>
+        <v>707.9</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>764</v>
+        <v>804</v>
       </c>
       <c r="C19" t="n">
-        <v>733</v>
+        <v>633</v>
       </c>
       <c r="D19" t="n">
-        <v>797</v>
+        <v>740</v>
       </c>
       <c r="E19" t="n">
-        <v>742</v>
+        <v>692</v>
       </c>
       <c r="F19" t="n">
-        <v>766</v>
+        <v>684</v>
       </c>
       <c r="G19" t="n">
-        <v>783</v>
+        <v>839</v>
       </c>
       <c r="H19" t="n">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="I19" t="n">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J19" t="n">
-        <v>746</v>
+        <v>717</v>
       </c>
       <c r="K19" t="n">
-        <v>686</v>
+        <v>712</v>
       </c>
       <c r="L19" t="n">
-        <v>763.6</v>
+        <v>744.5</v>
       </c>
     </row>
     <row r="20">
@@ -1158,34 +1158,34 @@
         <v>885</v>
       </c>
       <c r="C20" t="n">
-        <v>868</v>
+        <v>794</v>
       </c>
       <c r="D20" t="n">
-        <v>872</v>
+        <v>832</v>
       </c>
       <c r="E20" t="n">
-        <v>805</v>
+        <v>881</v>
       </c>
       <c r="F20" t="n">
-        <v>865</v>
+        <v>735</v>
       </c>
       <c r="G20" t="n">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="H20" t="n">
-        <v>952</v>
+        <v>777</v>
       </c>
       <c r="I20" t="n">
-        <v>944</v>
+        <v>748</v>
       </c>
       <c r="J20" t="n">
-        <v>974</v>
+        <v>824</v>
       </c>
       <c r="K20" t="n">
-        <v>922</v>
+        <v>876</v>
       </c>
       <c r="L20" t="n">
-        <v>886.8</v>
+        <v>814</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="C21" t="n">
-        <v>725</v>
+        <v>680</v>
       </c>
       <c r="D21" t="n">
-        <v>818</v>
+        <v>663</v>
       </c>
       <c r="E21" t="n">
-        <v>791</v>
+        <v>699</v>
       </c>
       <c r="F21" t="n">
-        <v>728</v>
+        <v>688</v>
       </c>
       <c r="G21" t="n">
-        <v>751</v>
+        <v>714</v>
       </c>
       <c r="H21" t="n">
-        <v>885</v>
+        <v>723</v>
       </c>
       <c r="I21" t="n">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="J21" t="n">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="K21" t="n">
-        <v>776</v>
+        <v>747</v>
       </c>
       <c r="L21" t="n">
-        <v>780.1</v>
+        <v>722.6</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="C22" t="n">
-        <v>718</v>
+        <v>647</v>
       </c>
       <c r="D22" t="n">
-        <v>851</v>
+        <v>613</v>
       </c>
       <c r="E22" t="n">
-        <v>753</v>
+        <v>677</v>
       </c>
       <c r="F22" t="n">
-        <v>743</v>
+        <v>661</v>
       </c>
       <c r="G22" t="n">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="H22" t="n">
-        <v>708</v>
+        <v>672</v>
       </c>
       <c r="I22" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="J22" t="n">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="K22" t="n">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="L22" t="n">
-        <v>724.1</v>
+        <v>665.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>787</v>
+        <v>683</v>
       </c>
       <c r="C23" t="n">
-        <v>726</v>
+        <v>616</v>
       </c>
       <c r="D23" t="n">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>628</v>
       </c>
       <c r="F23" t="n">
+        <v>624</v>
+      </c>
+      <c r="G23" t="n">
+        <v>619</v>
+      </c>
+      <c r="H23" t="n">
+        <v>725</v>
+      </c>
+      <c r="I23" t="n">
+        <v>580</v>
+      </c>
+      <c r="J23" t="n">
+        <v>713</v>
+      </c>
+      <c r="K23" t="n">
         <v>719</v>
       </c>
-      <c r="G23" t="n">
-        <v>697</v>
-      </c>
-      <c r="H23" t="n">
-        <v>710</v>
-      </c>
-      <c r="I23" t="n">
-        <v>721</v>
-      </c>
-      <c r="J23" t="n">
-        <v>664</v>
-      </c>
-      <c r="K23" t="n">
-        <v>850</v>
-      </c>
       <c r="L23" t="n">
-        <v>728.7</v>
+        <v>661.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>906</v>
+        <v>665</v>
       </c>
       <c r="C24" t="n">
-        <v>647</v>
+        <v>718</v>
       </c>
       <c r="D24" t="n">
-        <v>825</v>
+        <v>764</v>
       </c>
       <c r="E24" t="n">
-        <v>874</v>
+        <v>738</v>
       </c>
       <c r="F24" t="n">
-        <v>817</v>
+        <v>621</v>
       </c>
       <c r="G24" t="n">
-        <v>818</v>
+        <v>770</v>
       </c>
       <c r="H24" t="n">
-        <v>744</v>
+        <v>719</v>
       </c>
       <c r="I24" t="n">
-        <v>803</v>
+        <v>682</v>
       </c>
       <c r="J24" t="n">
-        <v>961</v>
+        <v>696</v>
       </c>
       <c r="K24" t="n">
-        <v>710</v>
+        <v>807</v>
       </c>
       <c r="L24" t="n">
-        <v>810.5</v>
+        <v>718</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>722</v>
+        <v>689</v>
       </c>
       <c r="C25" t="n">
         <v>720</v>
       </c>
       <c r="D25" t="n">
-        <v>667</v>
+        <v>599</v>
       </c>
       <c r="E25" t="n">
-        <v>735</v>
+        <v>648</v>
       </c>
       <c r="F25" t="n">
-        <v>788</v>
+        <v>647</v>
       </c>
       <c r="G25" t="n">
-        <v>676</v>
+        <v>732</v>
       </c>
       <c r="H25" t="n">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="I25" t="n">
-        <v>706</v>
+        <v>734</v>
       </c>
       <c r="J25" t="n">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="K25" t="n">
-        <v>791</v>
+        <v>652</v>
       </c>
       <c r="L25" t="n">
-        <v>731.2</v>
+        <v>690.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C26" t="n">
-        <v>795</v>
+        <v>741</v>
       </c>
       <c r="D26" t="n">
-        <v>705</v>
+        <v>727</v>
       </c>
       <c r="E26" t="n">
-        <v>711</v>
+        <v>772</v>
       </c>
       <c r="F26" t="n">
-        <v>747</v>
+        <v>769</v>
       </c>
       <c r="G26" t="n">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="H26" t="n">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="I26" t="n">
-        <v>800</v>
+        <v>718</v>
       </c>
       <c r="J26" t="n">
-        <v>644</v>
+        <v>794</v>
       </c>
       <c r="K26" t="n">
-        <v>878</v>
+        <v>803</v>
       </c>
       <c r="L26" t="n">
-        <v>752.2</v>
+        <v>760.6</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C27" t="n">
-        <v>665</v>
+        <v>635</v>
       </c>
       <c r="D27" t="n">
-        <v>695</v>
+        <v>605</v>
       </c>
       <c r="E27" t="n">
-        <v>686</v>
+        <v>587</v>
       </c>
       <c r="F27" t="n">
-        <v>606</v>
+        <v>654</v>
       </c>
       <c r="G27" t="n">
-        <v>649</v>
+        <v>615</v>
       </c>
       <c r="H27" t="n">
-        <v>657</v>
+        <v>584</v>
       </c>
       <c r="I27" t="n">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="J27" t="n">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="K27" t="n">
-        <v>664</v>
+        <v>776</v>
       </c>
       <c r="L27" t="n">
-        <v>671.4</v>
+        <v>643.1</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>717</v>
+        <v>645</v>
       </c>
       <c r="C28" t="n">
-        <v>686</v>
+        <v>864</v>
       </c>
       <c r="D28" t="n">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="E28" t="n">
-        <v>784</v>
+        <v>615</v>
       </c>
       <c r="F28" t="n">
-        <v>710</v>
+        <v>669</v>
       </c>
       <c r="G28" t="n">
-        <v>810</v>
+        <v>626</v>
       </c>
       <c r="H28" t="n">
-        <v>822</v>
+        <v>629</v>
       </c>
       <c r="I28" t="n">
-        <v>798</v>
+        <v>673</v>
       </c>
       <c r="J28" t="n">
-        <v>627</v>
+        <v>778</v>
       </c>
       <c r="K28" t="n">
-        <v>906</v>
+        <v>625</v>
       </c>
       <c r="L28" t="n">
-        <v>752.1</v>
+        <v>683.8</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>777</v>
+        <v>672</v>
       </c>
       <c r="C29" t="n">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="D29" t="n">
-        <v>714</v>
+        <v>606</v>
       </c>
       <c r="E29" t="n">
-        <v>743</v>
+        <v>649</v>
       </c>
       <c r="F29" t="n">
-        <v>650</v>
+        <v>673</v>
       </c>
       <c r="G29" t="n">
-        <v>681</v>
+        <v>771</v>
       </c>
       <c r="H29" t="n">
-        <v>692</v>
+        <v>648</v>
       </c>
       <c r="I29" t="n">
-        <v>655</v>
+        <v>673</v>
       </c>
       <c r="J29" t="n">
-        <v>610</v>
+        <v>776</v>
       </c>
       <c r="K29" t="n">
-        <v>677</v>
+        <v>789</v>
       </c>
       <c r="L29" t="n">
-        <v>699.3</v>
+        <v>705.7</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>755</v>
+        <v>690</v>
       </c>
       <c r="C30" t="n">
-        <v>771</v>
+        <v>709</v>
       </c>
       <c r="D30" t="n">
-        <v>734</v>
+        <v>585</v>
       </c>
       <c r="E30" t="n">
-        <v>698</v>
+        <v>844</v>
       </c>
       <c r="F30" t="n">
-        <v>638</v>
+        <v>620</v>
       </c>
       <c r="G30" t="n">
-        <v>802</v>
+        <v>703</v>
       </c>
       <c r="H30" t="n">
-        <v>759</v>
+        <v>643</v>
       </c>
       <c r="I30" t="n">
-        <v>773</v>
+        <v>644</v>
       </c>
       <c r="J30" t="n">
-        <v>709</v>
+        <v>655</v>
       </c>
       <c r="K30" t="n">
-        <v>757</v>
+        <v>714</v>
       </c>
       <c r="L30" t="n">
-        <v>739.6</v>
+        <v>680.7</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>776</v>
+        <v>852</v>
       </c>
       <c r="C31" t="n">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D31" t="n">
-        <v>866</v>
+        <v>780</v>
       </c>
       <c r="E31" t="n">
-        <v>867</v>
+        <v>740</v>
       </c>
       <c r="F31" t="n">
-        <v>794</v>
+        <v>722</v>
       </c>
       <c r="G31" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H31" t="n">
-        <v>902</v>
+        <v>760</v>
       </c>
       <c r="I31" t="n">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="J31" t="n">
-        <v>765</v>
+        <v>704</v>
       </c>
       <c r="K31" t="n">
-        <v>885</v>
+        <v>732</v>
       </c>
       <c r="L31" t="n">
-        <v>821.9</v>
+        <v>762.6</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>777</v>
+        <v>650</v>
       </c>
       <c r="C32" t="n">
-        <v>796</v>
+        <v>712</v>
       </c>
       <c r="D32" t="n">
-        <v>830</v>
+        <v>807</v>
       </c>
       <c r="E32" t="n">
-        <v>637</v>
+        <v>758</v>
       </c>
       <c r="F32" t="n">
-        <v>789</v>
+        <v>621</v>
       </c>
       <c r="G32" t="n">
-        <v>802</v>
+        <v>717</v>
       </c>
       <c r="H32" t="n">
-        <v>822</v>
+        <v>667</v>
       </c>
       <c r="I32" t="n">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="J32" t="n">
-        <v>760</v>
+        <v>694</v>
       </c>
       <c r="K32" t="n">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="L32" t="n">
-        <v>778.2</v>
+        <v>719.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>851</v>
+        <v>766</v>
       </c>
       <c r="C33" t="n">
-        <v>913</v>
+        <v>686</v>
       </c>
       <c r="D33" t="n">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="E33" t="n">
-        <v>660</v>
+        <v>888</v>
       </c>
       <c r="F33" t="n">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="G33" t="n">
-        <v>713</v>
+        <v>853</v>
       </c>
       <c r="H33" t="n">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="I33" t="n">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="J33" t="n">
-        <v>885</v>
+        <v>748</v>
       </c>
       <c r="K33" t="n">
-        <v>864</v>
+        <v>765</v>
       </c>
       <c r="L33" t="n">
-        <v>795.5</v>
+        <v>769.7</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
       <c r="C34" t="n">
-        <v>779</v>
+        <v>720</v>
       </c>
       <c r="D34" t="n">
-        <v>686</v>
+        <v>720</v>
       </c>
       <c r="E34" t="n">
-        <v>657</v>
+        <v>679</v>
       </c>
       <c r="F34" t="n">
-        <v>763</v>
+        <v>693</v>
       </c>
       <c r="G34" t="n">
-        <v>689</v>
+        <v>655</v>
       </c>
       <c r="H34" t="n">
-        <v>792</v>
+        <v>640</v>
       </c>
       <c r="I34" t="n">
-        <v>603</v>
+        <v>726</v>
       </c>
       <c r="J34" t="n">
-        <v>825</v>
+        <v>654</v>
       </c>
       <c r="K34" t="n">
-        <v>861</v>
+        <v>690</v>
       </c>
       <c r="L34" t="n">
-        <v>735.7</v>
+        <v>678.4</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="C35" t="n">
-        <v>568</v>
+        <v>638</v>
       </c>
       <c r="D35" t="n">
-        <v>765</v>
+        <v>653</v>
       </c>
       <c r="E35" t="n">
-        <v>549</v>
+        <v>661</v>
       </c>
       <c r="F35" t="n">
-        <v>619</v>
+        <v>666</v>
       </c>
       <c r="G35" t="n">
-        <v>742</v>
+        <v>612</v>
       </c>
       <c r="H35" t="n">
-        <v>765</v>
+        <v>582</v>
       </c>
       <c r="I35" t="n">
-        <v>658</v>
+        <v>600</v>
       </c>
       <c r="J35" t="n">
-        <v>680</v>
+        <v>590</v>
       </c>
       <c r="K35" t="n">
-        <v>625</v>
+        <v>602</v>
       </c>
       <c r="L35" t="n">
-        <v>668.2</v>
+        <v>633.3</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>847</v>
+        <v>690</v>
       </c>
       <c r="C36" t="n">
-        <v>734</v>
+        <v>752</v>
       </c>
       <c r="D36" t="n">
-        <v>855</v>
+        <v>725</v>
       </c>
       <c r="E36" t="n">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="F36" t="n">
-        <v>741</v>
+        <v>820</v>
       </c>
       <c r="G36" t="n">
-        <v>834</v>
+        <v>755</v>
       </c>
       <c r="H36" t="n">
-        <v>695</v>
+        <v>771</v>
       </c>
       <c r="I36" t="n">
-        <v>737</v>
+        <v>691</v>
       </c>
       <c r="J36" t="n">
-        <v>833</v>
+        <v>688</v>
       </c>
       <c r="K36" t="n">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="L36" t="n">
-        <v>775.6</v>
+        <v>732.5</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>873</v>
+        <v>820</v>
       </c>
       <c r="C37" t="n">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="D37" t="n">
-        <v>718</v>
+        <v>583</v>
       </c>
       <c r="E37" t="n">
-        <v>750</v>
+        <v>736</v>
       </c>
       <c r="F37" t="n">
-        <v>880</v>
+        <v>767</v>
       </c>
       <c r="G37" t="n">
+        <v>691</v>
+      </c>
+      <c r="H37" t="n">
+        <v>678</v>
+      </c>
+      <c r="I37" t="n">
         <v>676</v>
       </c>
-      <c r="H37" t="n">
-        <v>802</v>
-      </c>
-      <c r="I37" t="n">
-        <v>775</v>
-      </c>
       <c r="J37" t="n">
-        <v>740</v>
+        <v>640</v>
       </c>
       <c r="K37" t="n">
-        <v>835</v>
+        <v>776</v>
       </c>
       <c r="L37" t="n">
-        <v>777.5</v>
+        <v>708.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="C38" t="n">
-        <v>880</v>
+        <v>678</v>
       </c>
       <c r="D38" t="n">
-        <v>752</v>
+        <v>715</v>
       </c>
       <c r="E38" t="n">
-        <v>734</v>
+        <v>661</v>
       </c>
       <c r="F38" t="n">
-        <v>728</v>
+        <v>643</v>
       </c>
       <c r="G38" t="n">
-        <v>819</v>
+        <v>791</v>
       </c>
       <c r="H38" t="n">
-        <v>740</v>
+        <v>775</v>
       </c>
       <c r="I38" t="n">
-        <v>679</v>
+        <v>705</v>
       </c>
       <c r="J38" t="n">
-        <v>755</v>
+        <v>684</v>
       </c>
       <c r="K38" t="n">
-        <v>724</v>
+        <v>665</v>
       </c>
       <c r="L38" t="n">
-        <v>750.6</v>
+        <v>699.2</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>658</v>
+        <v>684</v>
       </c>
       <c r="C39" t="n">
-        <v>733</v>
+        <v>810</v>
       </c>
       <c r="D39" t="n">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="E39" t="n">
-        <v>618</v>
+        <v>663</v>
       </c>
       <c r="F39" t="n">
-        <v>614</v>
+        <v>648</v>
       </c>
       <c r="G39" t="n">
-        <v>644</v>
+        <v>599</v>
       </c>
       <c r="H39" t="n">
-        <v>554</v>
+        <v>623</v>
       </c>
       <c r="I39" t="n">
-        <v>731</v>
+        <v>677</v>
       </c>
       <c r="J39" t="n">
-        <v>642</v>
+        <v>698</v>
       </c>
       <c r="K39" t="n">
-        <v>738</v>
+        <v>620</v>
       </c>
       <c r="L39" t="n">
-        <v>660.1</v>
+        <v>667.7</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>752</v>
+        <v>905</v>
       </c>
       <c r="C40" t="n">
-        <v>863</v>
+        <v>766</v>
       </c>
       <c r="D40" t="n">
-        <v>771</v>
+        <v>731</v>
       </c>
       <c r="E40" t="n">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="F40" t="n">
-        <v>651</v>
+        <v>601</v>
       </c>
       <c r="G40" t="n">
-        <v>687</v>
+        <v>764</v>
       </c>
       <c r="H40" t="n">
-        <v>748</v>
+        <v>709</v>
       </c>
       <c r="I40" t="n">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="J40" t="n">
-        <v>896</v>
+        <v>788</v>
       </c>
       <c r="K40" t="n">
-        <v>747</v>
+        <v>822</v>
       </c>
       <c r="L40" t="n">
-        <v>771.4</v>
+        <v>767.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>640</v>
+        <v>720</v>
       </c>
       <c r="C41" t="n">
-        <v>687</v>
+        <v>764</v>
       </c>
       <c r="D41" t="n">
-        <v>764</v>
+        <v>624</v>
       </c>
       <c r="E41" t="n">
-        <v>701</v>
+        <v>824</v>
       </c>
       <c r="F41" t="n">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="G41" t="n">
-        <v>676</v>
+        <v>821</v>
       </c>
       <c r="H41" t="n">
-        <v>735</v>
+        <v>677</v>
       </c>
       <c r="I41" t="n">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="J41" t="n">
-        <v>688</v>
+        <v>734</v>
       </c>
       <c r="K41" t="n">
-        <v>677</v>
+        <v>769</v>
       </c>
       <c r="L41" t="n">
-        <v>693.1</v>
+        <v>729.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>742</v>
+        <v>690</v>
       </c>
       <c r="C42" t="n">
-        <v>766</v>
+        <v>710</v>
       </c>
       <c r="D42" t="n">
-        <v>707</v>
+        <v>750</v>
       </c>
       <c r="E42" t="n">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="F42" t="n">
-        <v>841</v>
+        <v>711</v>
       </c>
       <c r="G42" t="n">
-        <v>830</v>
+        <v>757</v>
       </c>
       <c r="H42" t="n">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="I42" t="n">
-        <v>785</v>
+        <v>803</v>
       </c>
       <c r="J42" t="n">
-        <v>1049</v>
+        <v>734</v>
       </c>
       <c r="K42" t="n">
-        <v>881</v>
+        <v>726</v>
       </c>
       <c r="L42" t="n">
-        <v>802.4</v>
+        <v>734.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>838</v>
+        <v>782</v>
       </c>
       <c r="C43" t="n">
-        <v>794</v>
+        <v>842</v>
       </c>
       <c r="D43" t="n">
-        <v>755</v>
+        <v>714</v>
       </c>
       <c r="E43" t="n">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="F43" t="n">
-        <v>809</v>
+        <v>691</v>
       </c>
       <c r="G43" t="n">
-        <v>936</v>
+        <v>743</v>
       </c>
       <c r="H43" t="n">
-        <v>835</v>
+        <v>771</v>
       </c>
       <c r="I43" t="n">
-        <v>892</v>
+        <v>833</v>
       </c>
       <c r="J43" t="n">
-        <v>758</v>
+        <v>801</v>
       </c>
       <c r="K43" t="n">
-        <v>849</v>
+        <v>760</v>
       </c>
       <c r="L43" t="n">
-        <v>821.6</v>
+        <v>768.2</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>645</v>
+        <v>807</v>
       </c>
       <c r="C44" t="n">
-        <v>737</v>
+        <v>715</v>
       </c>
       <c r="D44" t="n">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="E44" t="n">
-        <v>719</v>
+        <v>774</v>
       </c>
       <c r="F44" t="n">
-        <v>769</v>
+        <v>744</v>
       </c>
       <c r="G44" t="n">
-        <v>761</v>
+        <v>684</v>
       </c>
       <c r="H44" t="n">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="I44" t="n">
-        <v>626</v>
+        <v>672</v>
       </c>
       <c r="J44" t="n">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="K44" t="n">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="L44" t="n">
-        <v>708.2</v>
+        <v>721.9</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>948</v>
+        <v>801</v>
       </c>
       <c r="C45" t="n">
-        <v>730</v>
+        <v>699</v>
       </c>
       <c r="D45" t="n">
-        <v>819</v>
+        <v>782</v>
       </c>
       <c r="E45" t="n">
-        <v>684</v>
+        <v>640</v>
       </c>
       <c r="F45" t="n">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="G45" t="n">
-        <v>881</v>
+        <v>781</v>
       </c>
       <c r="H45" t="n">
-        <v>783</v>
+        <v>630</v>
       </c>
       <c r="I45" t="n">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="J45" t="n">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="K45" t="n">
-        <v>880</v>
+        <v>780</v>
       </c>
       <c r="L45" t="n">
-        <v>797.8</v>
+        <v>741.2</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>788</v>
+        <v>713</v>
       </c>
       <c r="C46" t="n">
-        <v>745</v>
+        <v>769</v>
       </c>
       <c r="D46" t="n">
-        <v>706</v>
+        <v>663</v>
       </c>
       <c r="E46" t="n">
-        <v>797</v>
+        <v>634</v>
       </c>
       <c r="F46" t="n">
-        <v>654</v>
+        <v>757</v>
       </c>
       <c r="G46" t="n">
-        <v>757</v>
+        <v>689</v>
       </c>
       <c r="H46" t="n">
-        <v>704</v>
+        <v>681</v>
       </c>
       <c r="I46" t="n">
-        <v>831</v>
+        <v>646</v>
       </c>
       <c r="J46" t="n">
-        <v>784</v>
+        <v>720</v>
       </c>
       <c r="K46" t="n">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="L46" t="n">
-        <v>755.4</v>
+        <v>707.8</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>740</v>
+        <v>674</v>
       </c>
       <c r="C47" t="n">
-        <v>801</v>
+        <v>582</v>
       </c>
       <c r="D47" t="n">
-        <v>665</v>
+        <v>581</v>
       </c>
       <c r="E47" t="n">
-        <v>565</v>
+        <v>673</v>
       </c>
       <c r="F47" t="n">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G47" t="n">
-        <v>602</v>
+        <v>570</v>
       </c>
       <c r="H47" t="n">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="I47" t="n">
-        <v>639</v>
+        <v>678</v>
       </c>
       <c r="J47" t="n">
-        <v>801</v>
+        <v>673</v>
       </c>
       <c r="K47" t="n">
-        <v>680</v>
+        <v>617</v>
       </c>
       <c r="L47" t="n">
-        <v>681.3</v>
+        <v>638.3</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>824</v>
+        <v>788</v>
       </c>
       <c r="C48" t="n">
-        <v>978</v>
+        <v>789</v>
       </c>
       <c r="D48" t="n">
-        <v>788</v>
+        <v>764</v>
       </c>
       <c r="E48" t="n">
-        <v>857</v>
+        <v>762</v>
       </c>
       <c r="F48" t="n">
-        <v>794</v>
+        <v>708</v>
       </c>
       <c r="G48" t="n">
-        <v>873</v>
+        <v>779</v>
       </c>
       <c r="H48" t="n">
-        <v>953</v>
+        <v>770</v>
       </c>
       <c r="I48" t="n">
-        <v>858</v>
+        <v>724</v>
       </c>
       <c r="J48" t="n">
-        <v>798</v>
+        <v>818</v>
       </c>
       <c r="K48" t="n">
-        <v>915</v>
+        <v>883</v>
       </c>
       <c r="L48" t="n">
-        <v>863.8</v>
+        <v>778.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>830</v>
+        <v>771</v>
       </c>
       <c r="C49" t="n">
-        <v>835</v>
+        <v>928</v>
       </c>
       <c r="D49" t="n">
-        <v>882</v>
+        <v>791</v>
       </c>
       <c r="E49" t="n">
-        <v>784</v>
+        <v>755</v>
       </c>
       <c r="F49" t="n">
-        <v>793</v>
+        <v>758</v>
       </c>
       <c r="G49" t="n">
-        <v>820</v>
+        <v>708</v>
       </c>
       <c r="H49" t="n">
-        <v>888</v>
+        <v>827</v>
       </c>
       <c r="I49" t="n">
-        <v>678</v>
+        <v>818</v>
       </c>
       <c r="J49" t="n">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="K49" t="n">
-        <v>808</v>
+        <v>783</v>
       </c>
       <c r="L49" t="n">
-        <v>810.9</v>
+        <v>794.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="C50" t="n">
-        <v>847</v>
+        <v>668</v>
       </c>
       <c r="D50" t="n">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="E50" t="n">
-        <v>657</v>
+        <v>790</v>
       </c>
       <c r="F50" t="n">
-        <v>801</v>
+        <v>699</v>
       </c>
       <c r="G50" t="n">
-        <v>726</v>
+        <v>685</v>
       </c>
       <c r="H50" t="n">
-        <v>853</v>
+        <v>698</v>
       </c>
       <c r="I50" t="n">
-        <v>769</v>
+        <v>683</v>
       </c>
       <c r="J50" t="n">
-        <v>827</v>
+        <v>693</v>
       </c>
       <c r="K50" t="n">
-        <v>810</v>
+        <v>741</v>
       </c>
       <c r="L50" t="n">
-        <v>774.6</v>
+        <v>708.9</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>925</v>
+        <v>728</v>
       </c>
       <c r="C51" t="n">
-        <v>703</v>
+        <v>786</v>
       </c>
       <c r="D51" t="n">
-        <v>744</v>
+        <v>673</v>
       </c>
       <c r="E51" t="n">
-        <v>873</v>
+        <v>695</v>
       </c>
       <c r="F51" t="n">
-        <v>713</v>
+        <v>801</v>
       </c>
       <c r="G51" t="n">
-        <v>859</v>
+        <v>645</v>
       </c>
       <c r="H51" t="n">
-        <v>818</v>
+        <v>783</v>
       </c>
       <c r="I51" t="n">
-        <v>760</v>
+        <v>620</v>
       </c>
       <c r="J51" t="n">
-        <v>830</v>
+        <v>735</v>
       </c>
       <c r="K51" t="n">
-        <v>865</v>
+        <v>778</v>
       </c>
       <c r="L51" t="n">
-        <v>809</v>
+        <v>724.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>752.24</v>
+        <v>726.5</v>
       </c>
       <c r="C52" t="n">
-        <v>757.12</v>
+        <v>719.72</v>
       </c>
       <c r="D52" t="n">
-        <v>743.46</v>
+        <v>696.02</v>
       </c>
       <c r="E52" t="n">
-        <v>737.24</v>
+        <v>710.86</v>
       </c>
       <c r="F52" t="n">
-        <v>734.5</v>
+        <v>701.0599999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>754.1</v>
+        <v>714.2</v>
       </c>
       <c r="H52" t="n">
-        <v>765.84</v>
+        <v>708.66</v>
       </c>
       <c r="I52" t="n">
-        <v>746.2</v>
+        <v>704.24</v>
       </c>
       <c r="J52" t="n">
-        <v>769.78</v>
+        <v>712.58</v>
       </c>
       <c r="K52" t="n">
-        <v>777.74</v>
+        <v>722.3200000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>753.822</v>
+        <v>711.6160000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5.603955984115601</v>
+        <v>3.88463568687439</v>
       </c>
       <c r="C2" t="n">
-        <v>4.530008316040039</v>
+        <v>4.229013442993164</v>
       </c>
       <c r="D2" t="n">
-        <v>4.581815719604492</v>
+        <v>4.332267284393311</v>
       </c>
       <c r="E2" t="n">
-        <v>4.082113265991211</v>
+        <v>4.20611310005188</v>
       </c>
       <c r="F2" t="n">
-        <v>4.005775213241577</v>
+        <v>5.266832590103149</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62222695350647</v>
+        <v>4.046483278274536</v>
       </c>
       <c r="H2" t="n">
-        <v>4.136454820632935</v>
+        <v>4.285608053207397</v>
       </c>
       <c r="I2" t="n">
-        <v>4.349424600601196</v>
+        <v>4.290592432022095</v>
       </c>
       <c r="J2" t="n">
-        <v>4.738428354263306</v>
+        <v>4.346442222595215</v>
       </c>
       <c r="K2" t="n">
-        <v>5.093530416488647</v>
+        <v>4.571384191513062</v>
       </c>
       <c r="L2" t="n">
-        <v>4.574373364448547</v>
+        <v>4.345937228202819</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.633197069168091</v>
+        <v>4.694626331329346</v>
       </c>
       <c r="C3" t="n">
-        <v>5.141525745391846</v>
+        <v>5.229710340499878</v>
       </c>
       <c r="D3" t="n">
-        <v>4.918949842453003</v>
+        <v>4.545946836471558</v>
       </c>
       <c r="E3" t="n">
-        <v>5.186814785003662</v>
+        <v>4.87311840057373</v>
       </c>
       <c r="F3" t="n">
-        <v>4.664133787155151</v>
+        <v>4.548940896987915</v>
       </c>
       <c r="G3" t="n">
-        <v>4.467125654220581</v>
+        <v>4.30455207824707</v>
       </c>
       <c r="H3" t="n">
-        <v>5.030198097229004</v>
+        <v>5.133418321609497</v>
       </c>
       <c r="I3" t="n">
-        <v>4.667101144790649</v>
+        <v>4.368894815444946</v>
       </c>
       <c r="J3" t="n">
-        <v>5.49397873878479</v>
+        <v>4.969386577606201</v>
       </c>
       <c r="K3" t="n">
-        <v>5.755344152450562</v>
+        <v>4.432713508605957</v>
       </c>
       <c r="L3" t="n">
-        <v>4.995836901664734</v>
+        <v>4.71013081073761</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>3.65168571472168</v>
+        <v>4.013999938964844</v>
       </c>
       <c r="C4" t="n">
-        <v>4.157422542572021</v>
+        <v>4.287374019622803</v>
       </c>
       <c r="D4" t="n">
-        <v>3.591858386993408</v>
+        <v>3.892949819564819</v>
       </c>
       <c r="E4" t="n">
-        <v>3.627735137939453</v>
+        <v>3.939483404159546</v>
       </c>
       <c r="F4" t="n">
-        <v>3.775878190994263</v>
+        <v>3.665677070617676</v>
       </c>
       <c r="G4" t="n">
-        <v>4.245677947998047</v>
+        <v>3.649245500564575</v>
       </c>
       <c r="H4" t="n">
-        <v>4.586315393447876</v>
+        <v>3.99787712097168</v>
       </c>
       <c r="I4" t="n">
-        <v>3.780847311019897</v>
+        <v>3.985374927520752</v>
       </c>
       <c r="J4" t="n">
-        <v>4.399767160415649</v>
+        <v>4.382358074188232</v>
       </c>
       <c r="K4" t="n">
-        <v>4.291566133499146</v>
+        <v>4.026772499084473</v>
       </c>
       <c r="L4" t="n">
-        <v>4.010875391960144</v>
+        <v>3.98411123752594</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.288567066192627</v>
+        <v>4.395835161209106</v>
       </c>
       <c r="C5" t="n">
-        <v>3.745938062667847</v>
+        <v>4.372402429580688</v>
       </c>
       <c r="D5" t="n">
-        <v>4.62120795249939</v>
+        <v>4.541403770446777</v>
       </c>
       <c r="E5" t="n">
-        <v>4.35787558555603</v>
+        <v>3.985156536102295</v>
       </c>
       <c r="F5" t="n">
-        <v>4.078141689300537</v>
+        <v>4.15893816947937</v>
       </c>
       <c r="G5" t="n">
-        <v>4.467614412307739</v>
+        <v>4.428493022918701</v>
       </c>
       <c r="H5" t="n">
-        <v>4.317516803741455</v>
+        <v>4.2567298412323</v>
       </c>
       <c r="I5" t="n">
-        <v>3.94494366645813</v>
+        <v>4.084587335586548</v>
       </c>
       <c r="J5" t="n">
-        <v>3.740974903106689</v>
+        <v>3.946974277496338</v>
       </c>
       <c r="K5" t="n">
-        <v>3.832239627838135</v>
+        <v>4.247195720672607</v>
       </c>
       <c r="L5" t="n">
-        <v>4.139501976966858</v>
+        <v>4.241771626472473</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.836722612380981</v>
+        <v>4.506765842437744</v>
       </c>
       <c r="C6" t="n">
-        <v>4.069625616073608</v>
+        <v>4.389881372451782</v>
       </c>
       <c r="D6" t="n">
-        <v>3.987839221954346</v>
+        <v>4.111979007720947</v>
       </c>
       <c r="E6" t="n">
-        <v>4.155405282974243</v>
+        <v>4.215077877044678</v>
       </c>
       <c r="F6" t="n">
-        <v>4.66513729095459</v>
+        <v>4.159703969955444</v>
       </c>
       <c r="G6" t="n">
-        <v>4.155407428741455</v>
+        <v>4.710771799087524</v>
       </c>
       <c r="H6" t="n">
-        <v>5.055131912231445</v>
+        <v>4.677103757858276</v>
       </c>
       <c r="I6" t="n">
-        <v>4.130965232849121</v>
+        <v>4.247786045074463</v>
       </c>
       <c r="J6" t="n">
-        <v>4.254664182662964</v>
+        <v>4.054393768310547</v>
       </c>
       <c r="K6" t="n">
-        <v>4.580843687057495</v>
+        <v>4.364677906036377</v>
       </c>
       <c r="L6" t="n">
-        <v>4.289174246788025</v>
+        <v>4.343814134597778</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.01676869392395</v>
+        <v>3.87216854095459</v>
       </c>
       <c r="C7" t="n">
-        <v>4.211309194564819</v>
+        <v>3.906562566757202</v>
       </c>
       <c r="D7" t="n">
-        <v>4.449666023254395</v>
+        <v>3.797392606735229</v>
       </c>
       <c r="E7" t="n">
-        <v>3.940464735031128</v>
+        <v>4.11306357383728</v>
       </c>
       <c r="F7" t="n">
-        <v>4.033246994018555</v>
+        <v>4.081156730651855</v>
       </c>
       <c r="G7" t="n">
-        <v>4.045674800872803</v>
+        <v>4.042795896530151</v>
       </c>
       <c r="H7" t="n">
-        <v>4.16540789604187</v>
+        <v>3.92351222038269</v>
       </c>
       <c r="I7" t="n">
-        <v>3.809293031692505</v>
+        <v>3.895453691482544</v>
       </c>
       <c r="J7" t="n">
-        <v>4.086575031280518</v>
+        <v>3.947018384933472</v>
       </c>
       <c r="K7" t="n">
-        <v>3.872648000717163</v>
+        <v>3.998825788497925</v>
       </c>
       <c r="L7" t="n">
-        <v>4.06310544013977</v>
+        <v>3.957795000076294</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.646142959594727</v>
+        <v>4.6949143409729</v>
       </c>
       <c r="C8" t="n">
-        <v>4.97830867767334</v>
+        <v>4.333992481231689</v>
       </c>
       <c r="D8" t="n">
-        <v>4.095469236373901</v>
+        <v>4.121031761169434</v>
       </c>
       <c r="E8" t="n">
-        <v>4.167200803756714</v>
+        <v>4.126754999160767</v>
       </c>
       <c r="F8" t="n">
-        <v>4.426648855209351</v>
+        <v>4.2766273021698</v>
       </c>
       <c r="G8" t="n">
-        <v>4.024738788604736</v>
+        <v>4.178863525390625</v>
       </c>
       <c r="H8" t="n">
-        <v>4.178351640701294</v>
+        <v>4.11240553855896</v>
       </c>
       <c r="I8" t="n">
-        <v>5.017224788665771</v>
+        <v>4.374659299850464</v>
       </c>
       <c r="J8" t="n">
-        <v>4.90100622177124</v>
+        <v>4.276961803436279</v>
       </c>
       <c r="K8" t="n">
-        <v>5.530404090881348</v>
+        <v>4.614028692245483</v>
       </c>
       <c r="L8" t="n">
-        <v>4.596549606323242</v>
+        <v>4.31102397441864</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.801316738128662</v>
+        <v>3.764294147491455</v>
       </c>
       <c r="C9" t="n">
-        <v>3.767878770828247</v>
+        <v>3.980194807052612</v>
       </c>
       <c r="D9" t="n">
-        <v>3.557948350906372</v>
+        <v>3.710872173309326</v>
       </c>
       <c r="E9" t="n">
-        <v>3.652694225311279</v>
+        <v>3.729812145233154</v>
       </c>
       <c r="F9" t="n">
-        <v>3.795317411422729</v>
+        <v>3.882397174835205</v>
       </c>
       <c r="G9" t="n">
-        <v>4.405765056610107</v>
+        <v>3.78319263458252</v>
       </c>
       <c r="H9" t="n">
-        <v>4.438676834106445</v>
+        <v>3.865461826324463</v>
       </c>
       <c r="I9" t="n">
-        <v>3.704058408737183</v>
+        <v>3.630561351776123</v>
       </c>
       <c r="J9" t="n">
-        <v>3.521569013595581</v>
+        <v>3.937357664108276</v>
       </c>
       <c r="K9" t="n">
-        <v>4.629731416702271</v>
+        <v>3.719823598861694</v>
       </c>
       <c r="L9" t="n">
-        <v>3.927495622634888</v>
+        <v>3.800396752357483</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.099510908126831</v>
+        <v>5.26186203956604</v>
       </c>
       <c r="C10" t="n">
-        <v>4.9055016040802</v>
+        <v>5.88172435760498</v>
       </c>
       <c r="D10" t="n">
-        <v>6.020669937133789</v>
+        <v>5.544620037078857</v>
       </c>
       <c r="E10" t="n">
-        <v>6.723300218582153</v>
+        <v>5.187548875808716</v>
       </c>
       <c r="F10" t="n">
-        <v>5.031913042068481</v>
+        <v>5.188050031661987</v>
       </c>
       <c r="G10" t="n">
-        <v>5.25031304359436</v>
+        <v>5.589507341384888</v>
       </c>
       <c r="H10" t="n">
-        <v>6.497599840164185</v>
+        <v>5.464337587356567</v>
       </c>
       <c r="I10" t="n">
-        <v>5.859756946563721</v>
+        <v>5.597093105316162</v>
       </c>
       <c r="J10" t="n">
-        <v>4.993065357208252</v>
+        <v>4.995287656784058</v>
       </c>
       <c r="K10" t="n">
-        <v>5.677732706069946</v>
+        <v>5.634769678115845</v>
       </c>
       <c r="L10" t="n">
-        <v>5.605936360359192</v>
+        <v>5.43448007106781</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.543667078018188</v>
+        <v>4.982334852218628</v>
       </c>
       <c r="C11" t="n">
-        <v>4.626484632492065</v>
+        <v>4.298246622085571</v>
       </c>
       <c r="D11" t="n">
-        <v>4.714237689971924</v>
+        <v>5.298275947570801</v>
       </c>
       <c r="E11" t="n">
-        <v>4.668875932693481</v>
+        <v>5.634927988052368</v>
       </c>
       <c r="F11" t="n">
-        <v>5.452340364456177</v>
+        <v>5.441911935806274</v>
       </c>
       <c r="G11" t="n">
-        <v>5.010974407196045</v>
+        <v>5.271843194961548</v>
       </c>
       <c r="H11" t="n">
-        <v>4.789030313491821</v>
+        <v>4.324265956878662</v>
       </c>
       <c r="I11" t="n">
-        <v>4.528226137161255</v>
+        <v>5.182057857513428</v>
       </c>
       <c r="J11" t="n">
-        <v>4.652895450592041</v>
+        <v>5.417377948760986</v>
       </c>
       <c r="K11" t="n">
-        <v>5.26782488822937</v>
+        <v>5.819495677947998</v>
       </c>
       <c r="L11" t="n">
-        <v>4.825455689430237</v>
+        <v>5.167073798179627</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.662862300872803</v>
+        <v>4.681854724884033</v>
       </c>
       <c r="C12" t="n">
-        <v>3.84413743019104</v>
+        <v>4.365131378173828</v>
       </c>
       <c r="D12" t="n">
-        <v>4.805780410766602</v>
+        <v>4.078134536743164</v>
       </c>
       <c r="E12" t="n">
-        <v>3.987318277359009</v>
+        <v>4.060662508010864</v>
       </c>
       <c r="F12" t="n">
-        <v>3.914520025253296</v>
+        <v>4.468157052993774</v>
       </c>
       <c r="G12" t="n">
-        <v>4.527471542358398</v>
+        <v>4.61854100227356</v>
       </c>
       <c r="H12" t="n">
-        <v>3.984345436096191</v>
+        <v>4.688379049301147</v>
       </c>
       <c r="I12" t="n">
-        <v>3.768930673599243</v>
+        <v>5.060930728912354</v>
       </c>
       <c r="J12" t="n">
-        <v>4.491807699203491</v>
+        <v>3.947257518768311</v>
       </c>
       <c r="K12" t="n">
-        <v>4.199943065643311</v>
+        <v>4.396566867828369</v>
       </c>
       <c r="L12" t="n">
-        <v>4.218711686134339</v>
+        <v>4.436561536788941</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5.265298128128052</v>
+        <v>7.167349338531494</v>
       </c>
       <c r="C13" t="n">
-        <v>5.149600267410278</v>
+        <v>5.469346523284912</v>
       </c>
       <c r="D13" t="n">
-        <v>4.517757177352905</v>
+        <v>5.77506685256958</v>
       </c>
       <c r="E13" t="n">
-        <v>5.023922204971313</v>
+        <v>5.763039588928223</v>
       </c>
       <c r="F13" t="n">
-        <v>4.498790740966797</v>
+        <v>5.461830854415894</v>
       </c>
       <c r="G13" t="n">
-        <v>4.424513339996338</v>
+        <v>5.787806987762451</v>
       </c>
       <c r="H13" t="n">
-        <v>4.940208435058594</v>
+        <v>6.420399904251099</v>
       </c>
       <c r="I13" t="n">
-        <v>6.392690658569336</v>
+        <v>5.992508411407471</v>
       </c>
       <c r="J13" t="n">
-        <v>5.197478771209717</v>
+        <v>4.879372358322144</v>
       </c>
       <c r="K13" t="n">
-        <v>5.000033855438232</v>
+        <v>5.153022050857544</v>
       </c>
       <c r="L13" t="n">
-        <v>5.041029357910157</v>
+        <v>5.786974287033081</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.464375019073486</v>
+        <v>4.362673997879028</v>
       </c>
       <c r="C14" t="n">
-        <v>4.236485004425049</v>
+        <v>4.418979644775391</v>
       </c>
       <c r="D14" t="n">
-        <v>4.074398994445801</v>
+        <v>4.099855184555054</v>
       </c>
       <c r="E14" t="n">
-        <v>4.186096429824829</v>
+        <v>4.434889078140259</v>
       </c>
       <c r="F14" t="n">
-        <v>5.042102098464966</v>
+        <v>4.167597770690918</v>
       </c>
       <c r="G14" t="n">
-        <v>4.64367413520813</v>
+        <v>4.330262422561646</v>
       </c>
       <c r="H14" t="n">
-        <v>4.988276958465576</v>
+        <v>4.200078010559082</v>
       </c>
       <c r="I14" t="n">
-        <v>4.904492616653442</v>
+        <v>4.302006959915161</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9274582862854</v>
+        <v>3.902583360671997</v>
       </c>
       <c r="K14" t="n">
-        <v>4.794275283813477</v>
+        <v>4.503868341445923</v>
       </c>
       <c r="L14" t="n">
-        <v>4.626163482666016</v>
+        <v>4.272279477119445</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>5.037166595458984</v>
+        <v>4.483407258987427</v>
       </c>
       <c r="C15" t="n">
-        <v>4.779815435409546</v>
+        <v>5.163612842559814</v>
       </c>
       <c r="D15" t="n">
-        <v>4.307521820068359</v>
+        <v>5.138155460357666</v>
       </c>
       <c r="E15" t="n">
-        <v>5.311947584152222</v>
+        <v>4.879836082458496</v>
       </c>
       <c r="F15" t="n">
-        <v>4.413748264312744</v>
+        <v>4.521493673324585</v>
       </c>
       <c r="G15" t="n">
-        <v>5.544388771057129</v>
+        <v>5.454161405563354</v>
       </c>
       <c r="H15" t="n">
-        <v>4.967856645584106</v>
+        <v>5.303062677383423</v>
       </c>
       <c r="I15" t="n">
-        <v>5.197768926620483</v>
+        <v>4.583341598510742</v>
       </c>
       <c r="J15" t="n">
-        <v>4.320474147796631</v>
+        <v>4.614253282546997</v>
       </c>
       <c r="K15" t="n">
-        <v>4.689541578292847</v>
+        <v>4.66889762878418</v>
       </c>
       <c r="L15" t="n">
-        <v>4.857022976875305</v>
+        <v>4.881022191047668</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.760915517807007</v>
+        <v>4.604056835174561</v>
       </c>
       <c r="C16" t="n">
-        <v>4.359392881393433</v>
+        <v>3.917310237884521</v>
       </c>
       <c r="D16" t="n">
-        <v>4.18833065032959</v>
+        <v>4.251209735870361</v>
       </c>
       <c r="E16" t="n">
-        <v>4.850182056427002</v>
+        <v>4.479889392852783</v>
       </c>
       <c r="F16" t="n">
-        <v>4.392307043075562</v>
+        <v>4.443431854248047</v>
       </c>
       <c r="G16" t="n">
-        <v>4.768831729888916</v>
+        <v>4.861342191696167</v>
       </c>
       <c r="H16" t="n">
-        <v>4.45672345161438</v>
+        <v>4.128983736038208</v>
       </c>
       <c r="I16" t="n">
-        <v>4.37883472442627</v>
+        <v>4.278633117675781</v>
       </c>
       <c r="J16" t="n">
-        <v>4.12000584602356</v>
+        <v>4.816730737686157</v>
       </c>
       <c r="K16" t="n">
-        <v>4.069135427474976</v>
+        <v>4.348365783691406</v>
       </c>
       <c r="L16" t="n">
-        <v>4.434465932846069</v>
+        <v>4.4129953622818</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.380851984024048</v>
+        <v>5.136658906936646</v>
       </c>
       <c r="C17" t="n">
-        <v>4.376325845718384</v>
+        <v>4.864354133605957</v>
       </c>
       <c r="D17" t="n">
-        <v>4.896995782852173</v>
+        <v>4.13579797744751</v>
       </c>
       <c r="E17" t="n">
-        <v>4.39980411529541</v>
+        <v>4.225311994552612</v>
       </c>
       <c r="F17" t="n">
-        <v>4.765866279602051</v>
+        <v>4.933207273483276</v>
       </c>
       <c r="G17" t="n">
-        <v>5.919456005096436</v>
+        <v>4.116065979003906</v>
       </c>
       <c r="H17" t="n">
-        <v>4.691565752029419</v>
+        <v>4.257163047790527</v>
       </c>
       <c r="I17" t="n">
-        <v>4.754398822784424</v>
+        <v>4.361908674240112</v>
       </c>
       <c r="J17" t="n">
-        <v>4.746430635452271</v>
+        <v>4.729142665863037</v>
       </c>
       <c r="K17" t="n">
-        <v>4.383841037750244</v>
+        <v>4.385849475860596</v>
       </c>
       <c r="L17" t="n">
-        <v>4.731553626060486</v>
+        <v>4.514546012878418</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.376842498779297</v>
+        <v>5.258644104003906</v>
       </c>
       <c r="C18" t="n">
-        <v>4.376849889755249</v>
+        <v>5.223289728164673</v>
       </c>
       <c r="D18" t="n">
-        <v>4.586826086044312</v>
+        <v>4.645271062850952</v>
       </c>
       <c r="E18" t="n">
-        <v>4.342931270599365</v>
+        <v>4.27764368057251</v>
       </c>
       <c r="F18" t="n">
-        <v>4.242189407348633</v>
+        <v>4.517009973526001</v>
       </c>
       <c r="G18" t="n">
-        <v>4.543925285339355</v>
+        <v>5.177345514297485</v>
       </c>
       <c r="H18" t="n">
-        <v>5.053624391555786</v>
+        <v>5.546914339065552</v>
       </c>
       <c r="I18" t="n">
-        <v>5.098532199859619</v>
+        <v>4.353464841842651</v>
       </c>
       <c r="J18" t="n">
-        <v>4.920958757400513</v>
+        <v>4.363930225372314</v>
       </c>
       <c r="K18" t="n">
-        <v>5.045127153396606</v>
+        <v>4.66215181350708</v>
       </c>
       <c r="L18" t="n">
-        <v>4.658780694007874</v>
+        <v>4.802566528320312</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>5.097556591033936</v>
+        <v>4.531511545181274</v>
       </c>
       <c r="C19" t="n">
-        <v>4.605260610580444</v>
+        <v>4.032751560211182</v>
       </c>
       <c r="D19" t="n">
-        <v>4.117019891738892</v>
+        <v>4.292598724365234</v>
       </c>
       <c r="E19" t="n">
-        <v>4.401775121688843</v>
+        <v>4.210270166397095</v>
       </c>
       <c r="F19" t="n">
-        <v>4.523960828781128</v>
+        <v>4.59782075881958</v>
       </c>
       <c r="G19" t="n">
-        <v>4.424724340438843</v>
+        <v>4.770889043807983</v>
       </c>
       <c r="H19" t="n">
-        <v>4.254653930664062</v>
+        <v>4.325175762176514</v>
       </c>
       <c r="I19" t="n">
-        <v>4.09001612663269</v>
+        <v>4.028767585754395</v>
       </c>
       <c r="J19" t="n">
-        <v>4.177835464477539</v>
+        <v>4.335649013519287</v>
       </c>
       <c r="K19" t="n">
-        <v>3.82874870300293</v>
+        <v>4.351439476013184</v>
       </c>
       <c r="L19" t="n">
-        <v>4.352155160903931</v>
+        <v>4.347687363624573</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.868132352828979</v>
+        <v>5.289099454879761</v>
       </c>
       <c r="C20" t="n">
-        <v>4.99725604057312</v>
+        <v>5.813218355178833</v>
       </c>
       <c r="D20" t="n">
-        <v>5.412298917770386</v>
+        <v>5.222726106643677</v>
       </c>
       <c r="E20" t="n">
-        <v>5.325912475585938</v>
+        <v>5.210755109786987</v>
       </c>
       <c r="F20" t="n">
-        <v>5.442114114761353</v>
+        <v>5.099626064300537</v>
       </c>
       <c r="G20" t="n">
-        <v>4.873085021972656</v>
+        <v>4.53801441192627</v>
       </c>
       <c r="H20" t="n">
-        <v>5.75830864906311</v>
+        <v>5.217170476913452</v>
       </c>
       <c r="I20" t="n">
-        <v>6.116904020309448</v>
+        <v>4.979366779327393</v>
       </c>
       <c r="J20" t="n">
-        <v>5.456098079681396</v>
+        <v>5.009416818618774</v>
       </c>
       <c r="K20" t="n">
-        <v>5.484548807144165</v>
+        <v>4.950652837753296</v>
       </c>
       <c r="L20" t="n">
-        <v>5.473465847969055</v>
+        <v>5.133004641532898</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>5.290015935897827</v>
+        <v>4.795051097869873</v>
       </c>
       <c r="C21" t="n">
-        <v>4.64018702507019</v>
+        <v>4.266621589660645</v>
       </c>
       <c r="D21" t="n">
-        <v>4.945914268493652</v>
+        <v>4.396826982498169</v>
       </c>
       <c r="E21" t="n">
-        <v>4.709483861923218</v>
+        <v>4.019768953323364</v>
       </c>
       <c r="F21" t="n">
-        <v>4.466109275817871</v>
+        <v>4.50009298324585</v>
       </c>
       <c r="G21" t="n">
-        <v>4.156898021697998</v>
+        <v>4.780248403549194</v>
       </c>
       <c r="H21" t="n">
-        <v>5.038674116134644</v>
+        <v>4.894467353820801</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7852942943573</v>
+        <v>4.883468627929688</v>
       </c>
       <c r="J21" t="n">
-        <v>4.238746166229248</v>
+        <v>4.683610200881958</v>
       </c>
       <c r="K21" t="n">
-        <v>4.326468706130981</v>
+        <v>4.587570428848267</v>
       </c>
       <c r="L21" t="n">
-        <v>4.659779167175293</v>
+        <v>4.580772662162781</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.103039979934692</v>
+        <v>5.223814487457275</v>
       </c>
       <c r="C22" t="n">
-        <v>4.826685190200806</v>
+        <v>4.564926624298096</v>
       </c>
       <c r="D22" t="n">
-        <v>5.134416341781616</v>
+        <v>4.444227457046509</v>
       </c>
       <c r="E22" t="n">
-        <v>4.491048336029053</v>
+        <v>4.670138835906982</v>
       </c>
       <c r="F22" t="n">
-        <v>4.630221128463745</v>
+        <v>4.759906530380249</v>
       </c>
       <c r="G22" t="n">
-        <v>4.709507703781128</v>
+        <v>5.003298997879028</v>
       </c>
       <c r="H22" t="n">
-        <v>4.597277164459229</v>
+        <v>4.410452365875244</v>
       </c>
       <c r="I22" t="n">
-        <v>4.664631843566895</v>
+        <v>4.458408355712891</v>
       </c>
       <c r="J22" t="n">
-        <v>4.53094482421875</v>
+        <v>4.815465450286865</v>
       </c>
       <c r="K22" t="n">
-        <v>4.358394145965576</v>
+        <v>4.614995241165161</v>
       </c>
       <c r="L22" t="n">
-        <v>4.604616665840149</v>
+        <v>4.69656343460083</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>5.445109367370605</v>
+        <v>4.023035287857056</v>
       </c>
       <c r="C23" t="n">
-        <v>4.732527732849121</v>
+        <v>3.846017360687256</v>
       </c>
       <c r="D23" t="n">
-        <v>4.68855619430542</v>
+        <v>4.382607936859131</v>
       </c>
       <c r="E23" t="n">
-        <v>5.068573713302612</v>
+        <v>4.424506664276123</v>
       </c>
       <c r="F23" t="n">
-        <v>4.518991708755493</v>
+        <v>4.130774259567261</v>
       </c>
       <c r="G23" t="n">
-        <v>4.116002082824707</v>
+        <v>4.093354940414429</v>
       </c>
       <c r="H23" t="n">
-        <v>4.347420454025269</v>
+        <v>4.571999788284302</v>
       </c>
       <c r="I23" t="n">
-        <v>5.239667654037476</v>
+        <v>4.411875247955322</v>
       </c>
       <c r="J23" t="n">
-        <v>4.698037147521973</v>
+        <v>4.389819622039795</v>
       </c>
       <c r="K23" t="n">
-        <v>5.295990705490112</v>
+        <v>5.202743291854858</v>
       </c>
       <c r="L23" t="n">
-        <v>4.815087676048279</v>
+        <v>4.347673439979554</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5.263087749481201</v>
+        <v>4.242707252502441</v>
       </c>
       <c r="C24" t="n">
-        <v>4.670101165771484</v>
+        <v>4.71451997756958</v>
       </c>
       <c r="D24" t="n">
-        <v>5.073707580566406</v>
+        <v>6.237893342971802</v>
       </c>
       <c r="E24" t="n">
-        <v>5.092510223388672</v>
+        <v>5.082768440246582</v>
       </c>
       <c r="F24" t="n">
-        <v>4.77038836479187</v>
+        <v>4.318265438079834</v>
       </c>
       <c r="G24" t="n">
-        <v>5.057611227035522</v>
+        <v>4.872854232788086</v>
       </c>
       <c r="H24" t="n">
-        <v>4.674624443054199</v>
+        <v>4.448456764221191</v>
       </c>
       <c r="I24" t="n">
-        <v>4.788286209106445</v>
+        <v>4.297300100326538</v>
       </c>
       <c r="J24" t="n">
-        <v>6.037152767181396</v>
+        <v>4.471931934356689</v>
       </c>
       <c r="K24" t="n">
-        <v>4.836674213409424</v>
+        <v>4.755408525466919</v>
       </c>
       <c r="L24" t="n">
-        <v>5.026414394378662</v>
+        <v>4.744210600852966</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.087106466293335</v>
+        <v>5.38280200958252</v>
       </c>
       <c r="C25" t="n">
-        <v>4.672106981277466</v>
+        <v>4.553452253341675</v>
       </c>
       <c r="D25" t="n">
-        <v>4.631714344024658</v>
+        <v>4.489087581634521</v>
       </c>
       <c r="E25" t="n">
-        <v>4.362385272979736</v>
+        <v>4.628210306167603</v>
       </c>
       <c r="F25" t="n">
-        <v>4.692543029785156</v>
+        <v>4.503041982650757</v>
       </c>
       <c r="G25" t="n">
-        <v>4.241208076477051</v>
+        <v>4.512912750244141</v>
       </c>
       <c r="H25" t="n">
-        <v>4.516975402832031</v>
+        <v>4.827724456787109</v>
       </c>
       <c r="I25" t="n">
-        <v>4.490053415298462</v>
+        <v>4.626261949539185</v>
       </c>
       <c r="J25" t="n">
-        <v>4.914947032928467</v>
+        <v>5.003304004669189</v>
       </c>
       <c r="K25" t="n">
-        <v>4.381840467453003</v>
+        <v>4.658170461654663</v>
       </c>
       <c r="L25" t="n">
-        <v>4.499088048934937</v>
+        <v>4.718496775627136</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.565859317779541</v>
+        <v>4.58493709564209</v>
       </c>
       <c r="C26" t="n">
-        <v>4.536127328872681</v>
+        <v>4.605298519134521</v>
       </c>
       <c r="D26" t="n">
-        <v>4.510766744613647</v>
+        <v>4.47711181640625</v>
       </c>
       <c r="E26" t="n">
-        <v>4.655515909194946</v>
+        <v>4.675603151321411</v>
       </c>
       <c r="F26" t="n">
-        <v>4.277644395828247</v>
+        <v>4.592912912368774</v>
       </c>
       <c r="G26" t="n">
-        <v>4.497023344039917</v>
+        <v>4.914760112762451</v>
       </c>
       <c r="H26" t="n">
-        <v>5.155359745025635</v>
+        <v>5.107900857925415</v>
       </c>
       <c r="I26" t="n">
-        <v>4.658636331558228</v>
+        <v>4.536554336547852</v>
       </c>
       <c r="J26" t="n">
-        <v>4.03970742225647</v>
+        <v>4.611264705657959</v>
       </c>
       <c r="K26" t="n">
-        <v>4.783806324005127</v>
+        <v>4.917430877685547</v>
       </c>
       <c r="L26" t="n">
-        <v>4.568044686317444</v>
+        <v>4.702377438545227</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>3.672146081924438</v>
+        <v>4.117797136306763</v>
       </c>
       <c r="C27" t="n">
-        <v>3.997815370559692</v>
+        <v>4.234037399291992</v>
       </c>
       <c r="D27" t="n">
-        <v>4.406768560409546</v>
+        <v>4.152372121810913</v>
       </c>
       <c r="E27" t="n">
-        <v>4.062637329101562</v>
+        <v>4.015453100204468</v>
       </c>
       <c r="F27" t="n">
-        <v>3.595846652984619</v>
+        <v>4.36141300201416</v>
       </c>
       <c r="G27" t="n">
-        <v>4.022760152816772</v>
+        <v>4.197335481643677</v>
       </c>
       <c r="H27" t="n">
-        <v>3.845720052719116</v>
+        <v>4.139161586761475</v>
       </c>
       <c r="I27" t="n">
-        <v>4.118995666503906</v>
+        <v>3.965895175933838</v>
       </c>
       <c r="J27" t="n">
-        <v>3.732990980148315</v>
+        <v>4.518504619598389</v>
       </c>
       <c r="K27" t="n">
-        <v>4.379834175109863</v>
+        <v>5.025222063064575</v>
       </c>
       <c r="L27" t="n">
-        <v>3.983551502227783</v>
+        <v>4.272719168663025</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.220236539840698</v>
+        <v>4.037240743637085</v>
       </c>
       <c r="C28" t="n">
-        <v>4.176383256912231</v>
+        <v>4.816732406616211</v>
       </c>
       <c r="D28" t="n">
-        <v>4.085105419158936</v>
+        <v>4.502046346664429</v>
       </c>
       <c r="E28" t="n">
-        <v>4.432719707489014</v>
+        <v>3.772899389266968</v>
       </c>
       <c r="F28" t="n">
-        <v>4.72751259803772</v>
+        <v>4.670132398605347</v>
       </c>
       <c r="G28" t="n">
-        <v>4.22822904586792</v>
+        <v>4.338226318359375</v>
       </c>
       <c r="H28" t="n">
-        <v>4.511989116668701</v>
+        <v>4.202163934707642</v>
       </c>
       <c r="I28" t="n">
-        <v>4.190323829650879</v>
+        <v>6.117053031921387</v>
       </c>
       <c r="J28" t="n">
-        <v>3.757442712783813</v>
+        <v>5.074583053588867</v>
       </c>
       <c r="K28" t="n">
-        <v>5.065079927444458</v>
+        <v>4.076635360717773</v>
       </c>
       <c r="L28" t="n">
-        <v>4.339502215385437</v>
+        <v>4.560771298408508</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.324536561965942</v>
+        <v>4.578829526901245</v>
       </c>
       <c r="C29" t="n">
-        <v>4.406243085861206</v>
+        <v>4.870109081268311</v>
       </c>
       <c r="D29" t="n">
-        <v>4.197312593460083</v>
+        <v>4.364378929138184</v>
       </c>
       <c r="E29" t="n">
-        <v>4.16538667678833</v>
+        <v>4.355291128158569</v>
       </c>
       <c r="F29" t="n">
-        <v>4.170368909835815</v>
+        <v>4.316287755966187</v>
       </c>
       <c r="G29" t="n">
-        <v>4.088558197021484</v>
+        <v>4.744178295135498</v>
       </c>
       <c r="H29" t="n">
-        <v>4.026744842529297</v>
+        <v>4.259458303451538</v>
       </c>
       <c r="I29" t="n">
-        <v>4.114031553268433</v>
+        <v>4.205068111419678</v>
       </c>
       <c r="J29" t="n">
-        <v>4.139946222305298</v>
+        <v>4.55768346786499</v>
       </c>
       <c r="K29" t="n">
-        <v>4.270108222961426</v>
+        <v>5.526161193847656</v>
       </c>
       <c r="L29" t="n">
-        <v>4.190323686599731</v>
+        <v>4.577744579315185</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.283083438873291</v>
+        <v>4.260458469390869</v>
       </c>
       <c r="C30" t="n">
-        <v>5.051691293716431</v>
+        <v>4.06842827796936</v>
       </c>
       <c r="D30" t="n">
-        <v>4.659152030944824</v>
+        <v>4.071640968322754</v>
       </c>
       <c r="E30" t="n">
-        <v>4.220236301422119</v>
+        <v>5.578188896179199</v>
       </c>
       <c r="F30" t="n">
-        <v>4.119038581848145</v>
+        <v>3.681927442550659</v>
       </c>
       <c r="G30" t="n">
-        <v>4.825219631195068</v>
+        <v>4.238027334213257</v>
       </c>
       <c r="H30" t="n">
-        <v>4.082597494125366</v>
+        <v>3.915346145629883</v>
       </c>
       <c r="I30" t="n">
-        <v>4.650660753250122</v>
+        <v>4.711249828338623</v>
       </c>
       <c r="J30" t="n">
-        <v>4.241183519363403</v>
+        <v>3.660474061965942</v>
       </c>
       <c r="K30" t="n">
-        <v>4.423728942871094</v>
+        <v>4.680345296859741</v>
       </c>
       <c r="L30" t="n">
-        <v>4.455659198760986</v>
+        <v>4.286608672142028</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.490063428878784</v>
+        <v>5.393342971801758</v>
       </c>
       <c r="C31" t="n">
-        <v>5.380311250686646</v>
+        <v>4.920955419540405</v>
       </c>
       <c r="D31" t="n">
-        <v>5.156349420547485</v>
+        <v>4.654671430587769</v>
       </c>
       <c r="E31" t="n">
-        <v>4.629199743270874</v>
+        <v>4.741410255432129</v>
       </c>
       <c r="F31" t="n">
-        <v>4.589298963546753</v>
+        <v>4.703535556793213</v>
       </c>
       <c r="G31" t="n">
-        <v>4.795775890350342</v>
+        <v>4.710506916046143</v>
       </c>
       <c r="H31" t="n">
-        <v>4.822727203369141</v>
+        <v>5.192779779434204</v>
       </c>
       <c r="I31" t="n">
-        <v>4.997283697128296</v>
+        <v>5.106505155563354</v>
       </c>
       <c r="J31" t="n">
-        <v>4.590325355529785</v>
+        <v>4.347428321838379</v>
       </c>
       <c r="K31" t="n">
-        <v>5.578277587890625</v>
+        <v>4.436686754226685</v>
       </c>
       <c r="L31" t="n">
-        <v>4.902961254119873</v>
+        <v>4.820782256126404</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.95239520072937</v>
+        <v>4.409775972366333</v>
       </c>
       <c r="C32" t="n">
-        <v>4.569844961166382</v>
+        <v>4.996483087539673</v>
       </c>
       <c r="D32" t="n">
-        <v>5.262096166610718</v>
+        <v>4.674347400665283</v>
       </c>
       <c r="E32" t="n">
-        <v>4.227225780487061</v>
+        <v>4.367141723632812</v>
       </c>
       <c r="F32" t="n">
-        <v>5.256114959716797</v>
+        <v>4.44295072555542</v>
       </c>
       <c r="G32" t="n">
-        <v>5.500003337860107</v>
+        <v>4.59308123588562</v>
       </c>
       <c r="H32" t="n">
-        <v>5.95987606048584</v>
+        <v>4.695807695388794</v>
       </c>
       <c r="I32" t="n">
-        <v>4.839637279510498</v>
+        <v>4.940171718597412</v>
       </c>
       <c r="J32" t="n">
-        <v>4.641238451004028</v>
+        <v>4.632965326309204</v>
       </c>
       <c r="K32" t="n">
-        <v>5.433668613433838</v>
+        <v>4.944892406463623</v>
       </c>
       <c r="L32" t="n">
-        <v>5.064210081100464</v>
+        <v>4.669761729240418</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.532955884933472</v>
+        <v>4.406777858734131</v>
       </c>
       <c r="C33" t="n">
-        <v>4.830730438232422</v>
+        <v>4.876817226409912</v>
       </c>
       <c r="D33" t="n">
-        <v>4.833684206008911</v>
+        <v>4.430725336074829</v>
       </c>
       <c r="E33" t="n">
-        <v>4.076107501983643</v>
+        <v>5.227683782577515</v>
       </c>
       <c r="F33" t="n">
-        <v>4.623197555541992</v>
+        <v>4.7144935131073</v>
       </c>
       <c r="G33" t="n">
-        <v>4.265634775161743</v>
+        <v>4.560382127761841</v>
       </c>
       <c r="H33" t="n">
-        <v>4.714476585388184</v>
+        <v>5.220598459243774</v>
       </c>
       <c r="I33" t="n">
-        <v>4.687570810317993</v>
+        <v>4.393602848052979</v>
       </c>
       <c r="J33" t="n">
-        <v>5.289532423019409</v>
+        <v>4.741217851638794</v>
       </c>
       <c r="K33" t="n">
-        <v>4.861122846603394</v>
+        <v>5.356094598770142</v>
       </c>
       <c r="L33" t="n">
-        <v>4.671501302719117</v>
+        <v>4.792839360237122</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.127975702285767</v>
+        <v>3.926317691802979</v>
       </c>
       <c r="C34" t="n">
-        <v>4.26366138458252</v>
+        <v>3.712511777877808</v>
       </c>
       <c r="D34" t="n">
-        <v>4.125006198883057</v>
+        <v>4.290605068206787</v>
       </c>
       <c r="E34" t="n">
-        <v>4.145966768264771</v>
+        <v>4.034733295440674</v>
       </c>
       <c r="F34" t="n">
-        <v>4.565381765365601</v>
+        <v>4.076142072677612</v>
       </c>
       <c r="G34" t="n">
-        <v>4.106034755706787</v>
+        <v>3.852424144744873</v>
       </c>
       <c r="H34" t="n">
-        <v>4.132959604263306</v>
+        <v>3.70986533164978</v>
       </c>
       <c r="I34" t="n">
-        <v>4.189337730407715</v>
+        <v>3.857335329055786</v>
       </c>
       <c r="J34" t="n">
-        <v>4.552891492843628</v>
+        <v>3.897388458251953</v>
       </c>
       <c r="K34" t="n">
-        <v>4.40477180480957</v>
+        <v>4.050275087356567</v>
       </c>
       <c r="L34" t="n">
-        <v>4.261398720741272</v>
+        <v>3.940759825706482</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.454159021377563</v>
+        <v>4.058008432388306</v>
       </c>
       <c r="C35" t="n">
-        <v>3.621788263320923</v>
+        <v>3.827051877975464</v>
       </c>
       <c r="D35" t="n">
-        <v>4.856606245040894</v>
+        <v>4.119793891906738</v>
       </c>
       <c r="E35" t="n">
-        <v>3.518048286437988</v>
+        <v>3.989865303039551</v>
       </c>
       <c r="F35" t="n">
-        <v>3.898054361343384</v>
+        <v>3.680636644363403</v>
       </c>
       <c r="G35" t="n">
-        <v>4.704021453857422</v>
+        <v>3.671171426773071</v>
       </c>
       <c r="H35" t="n">
-        <v>3.987834453582764</v>
+        <v>4.070632219314575</v>
       </c>
       <c r="I35" t="n">
-        <v>4.270615339279175</v>
+        <v>3.678445339202881</v>
       </c>
       <c r="J35" t="n">
-        <v>4.009792804718018</v>
+        <v>4.214062452316284</v>
       </c>
       <c r="K35" t="n">
-        <v>3.745940208435059</v>
+        <v>3.953728675842285</v>
       </c>
       <c r="L35" t="n">
-        <v>4.106686043739319</v>
+        <v>3.926339626312256</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>4.961363077163696</v>
+        <v>4.220065593719482</v>
       </c>
       <c r="C36" t="n">
-        <v>4.525971174240112</v>
+        <v>4.378623008728027</v>
       </c>
       <c r="D36" t="n">
-        <v>4.623225450515747</v>
+        <v>4.1941077709198</v>
       </c>
       <c r="E36" t="n">
-        <v>4.624215364456177</v>
+        <v>4.143765211105347</v>
       </c>
       <c r="F36" t="n">
-        <v>4.186322450637817</v>
+        <v>4.91074013710022</v>
       </c>
       <c r="G36" t="n">
-        <v>4.781836748123169</v>
+        <v>4.67485785484314</v>
       </c>
       <c r="H36" t="n">
-        <v>4.041737079620361</v>
+        <v>4.744054555892944</v>
       </c>
       <c r="I36" t="n">
-        <v>3.727991342544556</v>
+        <v>4.204068422317505</v>
       </c>
       <c r="J36" t="n">
-        <v>4.278630018234253</v>
+        <v>4.722824573516846</v>
       </c>
       <c r="K36" t="n">
-        <v>4.67162561416626</v>
+        <v>4.817766666412354</v>
       </c>
       <c r="L36" t="n">
-        <v>4.442291831970214</v>
+        <v>4.501087379455567</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.532413721084595</v>
+        <v>5.679093837738037</v>
       </c>
       <c r="C37" t="n">
-        <v>4.791778802871704</v>
+        <v>4.673558950424194</v>
       </c>
       <c r="D37" t="n">
-        <v>4.713478326797485</v>
+        <v>4.552422523498535</v>
       </c>
       <c r="E37" t="n">
-        <v>4.888099431991577</v>
+        <v>5.227060317993164</v>
       </c>
       <c r="F37" t="n">
-        <v>6.092501401901245</v>
+        <v>6.152158737182617</v>
       </c>
       <c r="G37" t="n">
-        <v>4.7967689037323</v>
+        <v>4.957831621170044</v>
       </c>
       <c r="H37" t="n">
-        <v>5.639143466949463</v>
+        <v>5.441257953643799</v>
       </c>
       <c r="I37" t="n">
-        <v>5.361818075180054</v>
+        <v>4.945164442062378</v>
       </c>
       <c r="J37" t="n">
-        <v>5.4845290184021</v>
+        <v>5.216497659683228</v>
       </c>
       <c r="K37" t="n">
-        <v>5.322919368743896</v>
+        <v>5.25989556312561</v>
       </c>
       <c r="L37" t="n">
-        <v>5.262345051765442</v>
+        <v>5.210494160652161</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>3.85127592086792</v>
+        <v>3.93848443031311</v>
       </c>
       <c r="C38" t="n">
-        <v>5.131972312927246</v>
+        <v>3.826596260070801</v>
       </c>
       <c r="D38" t="n">
-        <v>3.973382711410522</v>
+        <v>4.120047807693481</v>
       </c>
       <c r="E38" t="n">
-        <v>3.99782657623291</v>
+        <v>4.114872455596924</v>
       </c>
       <c r="F38" t="n">
-        <v>3.954910755157471</v>
+        <v>3.95744252204895</v>
       </c>
       <c r="G38" t="n">
-        <v>4.554957151412964</v>
+        <v>4.673657894134521</v>
       </c>
       <c r="H38" t="n">
-        <v>4.285590171813965</v>
+        <v>4.733449220657349</v>
       </c>
       <c r="I38" t="n">
-        <v>4.173874616622925</v>
+        <v>3.75995135307312</v>
       </c>
       <c r="J38" t="n">
-        <v>4.521492481231689</v>
+        <v>3.972178220748901</v>
       </c>
       <c r="K38" t="n">
-        <v>4.21326208114624</v>
+        <v>4.156200647354126</v>
       </c>
       <c r="L38" t="n">
-        <v>4.265854477882385</v>
+        <v>4.125288081169129</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.059633493423462</v>
+        <v>4.753221750259399</v>
       </c>
       <c r="C39" t="n">
-        <v>4.244180917739868</v>
+        <v>4.914708614349365</v>
       </c>
       <c r="D39" t="n">
-        <v>4.558401584625244</v>
+        <v>4.25383734703064</v>
       </c>
       <c r="E39" t="n">
-        <v>4.311508655548096</v>
+        <v>4.277673959732056</v>
       </c>
       <c r="F39" t="n">
-        <v>3.66515064239502</v>
+        <v>4.553946018218994</v>
       </c>
       <c r="G39" t="n">
-        <v>4.302044868469238</v>
+        <v>4.029756546020508</v>
       </c>
       <c r="H39" t="n">
-        <v>3.751463174819946</v>
+        <v>4.142131328582764</v>
       </c>
       <c r="I39" t="n">
-        <v>4.733402967453003</v>
+        <v>4.242013454437256</v>
       </c>
       <c r="J39" t="n">
-        <v>4.172131299972534</v>
+        <v>4.315286159515381</v>
       </c>
       <c r="K39" t="n">
-        <v>4.228005170822144</v>
+        <v>4.090873003005981</v>
       </c>
       <c r="L39" t="n">
-        <v>4.202592277526856</v>
+        <v>4.357344818115235</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.803488731384277</v>
+        <v>5.835040807723999</v>
       </c>
       <c r="C40" t="n">
-        <v>5.094244003295898</v>
+        <v>4.513794898986816</v>
       </c>
       <c r="D40" t="n">
-        <v>4.317276954650879</v>
+        <v>4.598063468933105</v>
       </c>
       <c r="E40" t="n">
-        <v>4.786530733108521</v>
+        <v>5.715540170669556</v>
       </c>
       <c r="F40" t="n">
-        <v>4.43245530128479</v>
+        <v>4.676565885543823</v>
       </c>
       <c r="G40" t="n">
-        <v>4.096851110458374</v>
+        <v>5.009689569473267</v>
       </c>
       <c r="H40" t="n">
-        <v>4.615993022918701</v>
+        <v>4.791487693786621</v>
       </c>
       <c r="I40" t="n">
-        <v>5.066788911819458</v>
+        <v>5.124784231185913</v>
       </c>
       <c r="J40" t="n">
-        <v>5.433379411697388</v>
+        <v>5.057877779006958</v>
       </c>
       <c r="K40" t="n">
-        <v>4.657888650894165</v>
+        <v>5.11525297164917</v>
       </c>
       <c r="L40" t="n">
-        <v>4.730489683151245</v>
+        <v>5.043809747695922</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.123768329620361</v>
+        <v>4.844937801361084</v>
       </c>
       <c r="C41" t="n">
-        <v>4.27338981628418</v>
+        <v>4.875686645507812</v>
       </c>
       <c r="D41" t="n">
-        <v>4.328249216079712</v>
+        <v>4.712587594985962</v>
       </c>
       <c r="E41" t="n">
-        <v>3.907355070114136</v>
+        <v>5.332293510437012</v>
       </c>
       <c r="F41" t="n">
-        <v>4.276362657546997</v>
+        <v>4.758171319961548</v>
       </c>
       <c r="G41" t="n">
-        <v>3.993603467941284</v>
+        <v>4.896765232086182</v>
       </c>
       <c r="H41" t="n">
-        <v>4.654876470565796</v>
+        <v>4.288349151611328</v>
       </c>
       <c r="I41" t="n">
-        <v>4.610001802444458</v>
+        <v>4.343895435333252</v>
       </c>
       <c r="J41" t="n">
-        <v>4.39656138420105</v>
+        <v>4.797540903091431</v>
       </c>
       <c r="K41" t="n">
-        <v>4.273380756378174</v>
+        <v>4.849453687667847</v>
       </c>
       <c r="L41" t="n">
-        <v>4.283754897117615</v>
+        <v>4.769968128204345</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.69631290435791</v>
+        <v>4.800365686416626</v>
       </c>
       <c r="C42" t="n">
-        <v>4.511779308319092</v>
+        <v>4.389504909515381</v>
       </c>
       <c r="D42" t="n">
-        <v>4.58112645149231</v>
+        <v>4.629321098327637</v>
       </c>
       <c r="E42" t="n">
-        <v>4.756141662597656</v>
+        <v>5.088300704956055</v>
       </c>
       <c r="F42" t="n">
-        <v>5.132146596908569</v>
+        <v>5.214332580566406</v>
       </c>
       <c r="G42" t="n">
-        <v>4.732178449630737</v>
+        <v>5.25337028503418</v>
       </c>
       <c r="H42" t="n">
-        <v>4.625459909439087</v>
+        <v>4.777594804763794</v>
       </c>
       <c r="I42" t="n">
-        <v>5.128170013427734</v>
+        <v>4.31329345703125</v>
       </c>
       <c r="J42" t="n">
-        <v>5.785932540893555</v>
+        <v>4.575815200805664</v>
       </c>
       <c r="K42" t="n">
-        <v>5.720628023147583</v>
+        <v>4.971633195877075</v>
       </c>
       <c r="L42" t="n">
-        <v>4.966987586021423</v>
+        <v>4.801353192329406</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.746164798736572</v>
+        <v>5.687243938446045</v>
       </c>
       <c r="C43" t="n">
-        <v>5.155085325241089</v>
+        <v>5.033411264419556</v>
       </c>
       <c r="D43" t="n">
-        <v>5.026915311813354</v>
+        <v>4.805001258850098</v>
       </c>
       <c r="E43" t="n">
-        <v>4.590561866760254</v>
+        <v>4.281379222869873</v>
       </c>
       <c r="F43" t="n">
-        <v>4.629471778869629</v>
+        <v>4.752659797668457</v>
       </c>
       <c r="G43" t="n">
-        <v>5.170030832290649</v>
+        <v>4.873327732086182</v>
       </c>
       <c r="H43" t="n">
-        <v>4.386575698852539</v>
+        <v>5.206462621688843</v>
       </c>
       <c r="I43" t="n">
-        <v>4.795509338378906</v>
+        <v>5.714629173278809</v>
       </c>
       <c r="J43" t="n">
-        <v>4.445463895797729</v>
+        <v>5.589801788330078</v>
       </c>
       <c r="K43" t="n">
-        <v>4.045989990234375</v>
+        <v>5.273250818252563</v>
       </c>
       <c r="L43" t="n">
-        <v>4.699176883697509</v>
+        <v>5.121716761589051</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.612002372741699</v>
+        <v>4.870184421539307</v>
       </c>
       <c r="C44" t="n">
-        <v>4.398566246032715</v>
+        <v>4.919843435287476</v>
       </c>
       <c r="D44" t="n">
-        <v>4.22999382019043</v>
+        <v>4.559805631637573</v>
       </c>
       <c r="E44" t="n">
-        <v>4.648875713348389</v>
+        <v>4.462578535079956</v>
       </c>
       <c r="F44" t="n">
-        <v>4.743653774261475</v>
+        <v>4.556326866149902</v>
       </c>
       <c r="G44" t="n">
-        <v>4.590558290481567</v>
+        <v>4.379289388656616</v>
       </c>
       <c r="H44" t="n">
-        <v>4.359657287597656</v>
+        <v>4.595724582672119</v>
       </c>
       <c r="I44" t="n">
-        <v>4.519749402999878</v>
+        <v>4.374143838882446</v>
       </c>
       <c r="J44" t="n">
-        <v>4.577083826065063</v>
+        <v>4.798182249069214</v>
       </c>
       <c r="K44" t="n">
-        <v>4.100810050964355</v>
+        <v>4.375298738479614</v>
       </c>
       <c r="L44" t="n">
-        <v>4.478095078468323</v>
+        <v>4.589137768745422</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.852371454238892</v>
+        <v>3.954424858093262</v>
       </c>
       <c r="C45" t="n">
-        <v>3.554747343063354</v>
+        <v>4.015893936157227</v>
       </c>
       <c r="D45" t="n">
-        <v>4.026526212692261</v>
+        <v>4.299502372741699</v>
       </c>
       <c r="E45" t="n">
-        <v>3.721832752227783</v>
+        <v>3.792870998382568</v>
       </c>
       <c r="F45" t="n">
-        <v>4.208045959472656</v>
+        <v>4.466055870056152</v>
       </c>
       <c r="G45" t="n">
-        <v>4.206052303314209</v>
+        <v>4.306484699249268</v>
       </c>
       <c r="H45" t="n">
-        <v>4.111793279647827</v>
+        <v>3.921511888504028</v>
       </c>
       <c r="I45" t="n">
-        <v>4.219656705856323</v>
+        <v>3.995408773422241</v>
       </c>
       <c r="J45" t="n">
-        <v>4.280363321304321</v>
+        <v>4.061223030090332</v>
       </c>
       <c r="K45" t="n">
-        <v>4.345184087753296</v>
+        <v>4.34537935256958</v>
       </c>
       <c r="L45" t="n">
-        <v>4.152657341957092</v>
+        <v>4.115875577926635</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.488816499710083</v>
+        <v>4.724366188049316</v>
       </c>
       <c r="C46" t="n">
-        <v>4.818470001220703</v>
+        <v>5.202187538146973</v>
       </c>
       <c r="D46" t="n">
-        <v>4.197094202041626</v>
+        <v>5.022568464279175</v>
       </c>
       <c r="E46" t="n">
-        <v>5.302728176116943</v>
+        <v>4.466070175170898</v>
       </c>
       <c r="F46" t="n">
-        <v>4.650892496109009</v>
+        <v>4.516920566558838</v>
       </c>
       <c r="G46" t="n">
-        <v>4.510741233825684</v>
+        <v>5.095373630523682</v>
       </c>
       <c r="H46" t="n">
-        <v>4.171139478683472</v>
+        <v>4.736334562301636</v>
       </c>
       <c r="I46" t="n">
-        <v>4.906916856765747</v>
+        <v>4.35136342048645</v>
       </c>
       <c r="J46" t="n">
-        <v>4.579626083374023</v>
+        <v>4.629619359970093</v>
       </c>
       <c r="K46" t="n">
-        <v>4.797527074813843</v>
+        <v>4.993645429611206</v>
       </c>
       <c r="L46" t="n">
-        <v>4.642395210266113</v>
+        <v>4.773844933509826</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.310269832611084</v>
+        <v>4.270580053329468</v>
       </c>
       <c r="C47" t="n">
-        <v>4.853896379470825</v>
+        <v>3.979358673095703</v>
       </c>
       <c r="D47" t="n">
-        <v>3.781158685684204</v>
+        <v>4.133957386016846</v>
       </c>
       <c r="E47" t="n">
-        <v>3.814061880111694</v>
+        <v>3.976365804672241</v>
       </c>
       <c r="F47" t="n">
-        <v>4.011610984802246</v>
+        <v>4.592718124389648</v>
       </c>
       <c r="G47" t="n">
-        <v>3.576195955276489</v>
+        <v>4.224702596664429</v>
       </c>
       <c r="H47" t="n">
-        <v>4.18315052986145</v>
+        <v>5.097368478775024</v>
       </c>
       <c r="I47" t="n">
-        <v>3.815086364746094</v>
+        <v>4.770257472991943</v>
       </c>
       <c r="J47" t="n">
-        <v>4.391567230224609</v>
+        <v>5.0666823387146</v>
       </c>
       <c r="K47" t="n">
-        <v>3.850970268249512</v>
+        <v>4.507745742797852</v>
       </c>
       <c r="L47" t="n">
-        <v>4.058796811103821</v>
+        <v>4.461973667144775</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.700272560119629</v>
+        <v>5.231988668441772</v>
       </c>
       <c r="C48" t="n">
-        <v>5.988440752029419</v>
+        <v>5.435023069381714</v>
       </c>
       <c r="D48" t="n">
-        <v>4.520743608474731</v>
+        <v>4.825786113739014</v>
       </c>
       <c r="E48" t="n">
-        <v>4.618986368179321</v>
+        <v>5.244740724563599</v>
       </c>
       <c r="F48" t="n">
-        <v>4.899770498275757</v>
+        <v>4.692988395690918</v>
       </c>
       <c r="G48" t="n">
-        <v>4.77058482170105</v>
+        <v>4.585527181625366</v>
       </c>
       <c r="H48" t="n">
-        <v>5.808885335922241</v>
+        <v>4.680163383483887</v>
       </c>
       <c r="I48" t="n">
-        <v>5.210436820983887</v>
+        <v>5.001778364181519</v>
       </c>
       <c r="J48" t="n">
-        <v>5.129158496856689</v>
+        <v>4.905514478683472</v>
       </c>
       <c r="K48" t="n">
-        <v>5.333622455596924</v>
+        <v>5.110515117645264</v>
       </c>
       <c r="L48" t="n">
-        <v>5.098090171813965</v>
+        <v>4.971402549743653</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.934658527374268</v>
+        <v>4.296006917953491</v>
       </c>
       <c r="C49" t="n">
-        <v>4.408532857894897</v>
+        <v>4.908032894134521</v>
       </c>
       <c r="D49" t="n">
-        <v>5.566511154174805</v>
+        <v>5.47249960899353</v>
       </c>
       <c r="E49" t="n">
-        <v>5.737393140792847</v>
+        <v>4.687564849853516</v>
       </c>
       <c r="F49" t="n">
-        <v>4.509792804718018</v>
+        <v>4.729033470153809</v>
       </c>
       <c r="G49" t="n">
-        <v>4.522710084915161</v>
+        <v>4.371889352798462</v>
       </c>
       <c r="H49" t="n">
-        <v>4.806495666503906</v>
+        <v>5.317557096481323</v>
       </c>
       <c r="I49" t="n">
-        <v>4.245440244674683</v>
+        <v>5.511482954025269</v>
       </c>
       <c r="J49" t="n">
-        <v>4.426471471786499</v>
+        <v>5.357875823974609</v>
       </c>
       <c r="K49" t="n">
-        <v>4.537691354751587</v>
+        <v>5.079580307006836</v>
       </c>
       <c r="L49" t="n">
-        <v>4.769569730758667</v>
+        <v>4.973152327537536</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>4.032532691955566</v>
+        <v>4.115873336791992</v>
       </c>
       <c r="C50" t="n">
-        <v>4.660374879837036</v>
+        <v>4.648597002029419</v>
       </c>
       <c r="D50" t="n">
-        <v>4.228982448577881</v>
+        <v>4.667554616928101</v>
       </c>
       <c r="E50" t="n">
-        <v>3.816074848175049</v>
+        <v>4.510951995849609</v>
       </c>
       <c r="F50" t="n">
-        <v>4.737686634063721</v>
+        <v>4.168018341064453</v>
       </c>
       <c r="G50" t="n">
-        <v>4.525738000869751</v>
+        <v>4.626073837280273</v>
       </c>
       <c r="H50" t="n">
-        <v>4.714239597320557</v>
+        <v>5.568078994750977</v>
       </c>
       <c r="I50" t="n">
-        <v>4.300286293029785</v>
+        <v>4.325376033782959</v>
       </c>
       <c r="J50" t="n">
-        <v>5.038882493972778</v>
+        <v>4.403052091598511</v>
       </c>
       <c r="K50" t="n">
-        <v>4.660855054855347</v>
+        <v>5.074178695678711</v>
       </c>
       <c r="L50" t="n">
-        <v>4.471565294265747</v>
+        <v>4.610775494575501</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>5.832314252853394</v>
+        <v>4.920584201812744</v>
       </c>
       <c r="C51" t="n">
-        <v>4.043462038040161</v>
+        <v>4.741512298583984</v>
       </c>
       <c r="D51" t="n">
-        <v>4.10581374168396</v>
+        <v>4.535665512084961</v>
       </c>
       <c r="E51" t="n">
-        <v>5.679726600646973</v>
+        <v>5.087790250778198</v>
       </c>
       <c r="F51" t="n">
-        <v>4.647909641265869</v>
+        <v>5.278959512710571</v>
       </c>
       <c r="G51" t="n">
-        <v>4.668402671813965</v>
+        <v>4.40099835395813</v>
       </c>
       <c r="H51" t="n">
-        <v>5.265295028686523</v>
+        <v>4.649417400360107</v>
       </c>
       <c r="I51" t="n">
-        <v>4.49083423614502</v>
+        <v>4.28974461555481</v>
       </c>
       <c r="J51" t="n">
-        <v>4.832411050796509</v>
+        <v>4.984293699264526</v>
       </c>
       <c r="K51" t="n">
-        <v>4.671335458755493</v>
+        <v>4.779086828231812</v>
       </c>
       <c r="L51" t="n">
-        <v>4.823750472068786</v>
+        <v>4.766805267333984</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.607699313163757</v>
+        <v>4.663401031494141</v>
       </c>
       <c r="C52" t="n">
-        <v>4.553804469108582</v>
+        <v>4.590147862434387</v>
       </c>
       <c r="D52" t="n">
-        <v>4.535852565765381</v>
+        <v>4.532132401466369</v>
       </c>
       <c r="E52" t="n">
-        <v>4.509026675224304</v>
+        <v>4.550936732292175</v>
       </c>
       <c r="F52" t="n">
-        <v>4.496870565414429</v>
+        <v>4.566199250221253</v>
       </c>
       <c r="G52" t="n">
-        <v>4.549586625099182</v>
+        <v>4.582050714492798</v>
       </c>
       <c r="H52" t="n">
-        <v>4.642539982795715</v>
+        <v>4.649716119766236</v>
       </c>
       <c r="I52" t="n">
-        <v>4.609708008766174</v>
+        <v>4.541090803146362</v>
       </c>
       <c r="J52" t="n">
-        <v>4.606600708961487</v>
+        <v>4.578917264938354</v>
       </c>
       <c r="K52" t="n">
-        <v>4.672089247703552</v>
+        <v>4.688732371330262</v>
       </c>
       <c r="L52" t="n">
-        <v>4.578377816200256</v>
+        <v>4.594332455158233</v>
       </c>
     </row>
   </sheetData>
